--- a/docs/data/jp/xlsx/8421.xlsx
+++ b/docs/data/jp/xlsx/8421.xlsx
@@ -1156,7 +1156,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>신금중앙금고 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>Ordinary Income BNK</t>
+          <t>경상수익</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
@@ -5866,7 +5866,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>Interest Income OIBNK</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="C82" s="20" t="n">
@@ -5924,7 +5924,7 @@
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>Interest On Loans And Discounts OIBNK</t>
+          <t>(이 중 대출금 이자)</t>
         </is>
       </c>
       <c r="C83" s="20" t="n">
@@ -5982,7 +5982,7 @@
     <row r="84">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>Interest And Dividends On Securities OIBNK</t>
+          <t>(이 중 유가증권 이자·배당금)</t>
         </is>
       </c>
       <c r="C84" s="20" t="n">
@@ -6040,7 +6040,7 @@
     <row r="85">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>Trust Fees BNK</t>
+          <t>신탁보수</t>
         </is>
       </c>
       <c r="C85" s="20" t="n">
@@ -6098,7 +6098,7 @@
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>Fees And Commissions OIBNK</t>
+          <t>용역거래 수익</t>
         </is>
       </c>
       <c r="C86" s="20" t="n">
@@ -6156,7 +6156,7 @@
     <row r="87">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>Trading Income OIBNK</t>
+          <t>특정거래 수익</t>
         </is>
       </c>
       <c r="C87" s="20" t="n">
@@ -6214,7 +6214,7 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>Other Ordinary Income OIBNK</t>
+          <t>기타 업무수익</t>
         </is>
       </c>
       <c r="C88" s="20" t="n">
@@ -6272,7 +6272,7 @@
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>Other Income OIBNK</t>
+          <t>기타 경상수익</t>
         </is>
       </c>
       <c r="C89" s="20" t="n">
@@ -6330,7 +6330,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Ordinary Expenses BNK</t>
+          <t>경상비용</t>
         </is>
       </c>
       <c r="C90" s="20" t="n">
@@ -6446,7 +6446,7 @@
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>Interest On Deposits OEBNK</t>
+          <t>(이 중 예금 이자)</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
@@ -6504,7 +6504,7 @@
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>Interest On Debentures BNK</t>
+          <t>(이 중 채권이자)</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
@@ -6562,7 +6562,7 @@
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>Fees And Commissions Payments OEBNK</t>
+          <t>용역거래 비용</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
@@ -6620,7 +6620,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Trading Expenses OEBNK</t>
+          <t>특정거래 비용</t>
         </is>
       </c>
       <c r="C95" s="20" t="n">
@@ -6678,7 +6678,7 @@
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>Other Ordinary Expenses OEBNK</t>
+          <t>기타 업무비용</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
@@ -6736,7 +6736,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>경비</t>
         </is>
       </c>
       <c r="E97" s="20" t="n">
@@ -6776,7 +6776,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Other Expenses OEBNK</t>
+          <t>기타 경상비용</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
@@ -6950,7 +6950,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Gain On Disposal Of Noncurrent Assets EI</t>
+          <t>고정자산 처분이익</t>
         </is>
       </c>
       <c r="D101" s="20" t="n">
@@ -7088,7 +7088,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Transfer To Reserve For Financial Products Transaction Liabilities ELBNK</t>
+          <t>금융상품거래 책임준비금 전입액</t>
         </is>
       </c>
       <c r="C104" s="20" t="n">
@@ -7796,7 +7796,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Other Comprehensive Income</t>
+          <t>기타포괄손익</t>
         </is>
       </c>
       <c r="C116" s="20" t="n">
@@ -8446,7 +8446,7 @@
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>부문 · Ordinary Income BNK</t>
+          <t>신금중앙금고 사업 · 경상수익</t>
         </is>
       </c>
       <c r="E127" s="20" t="n">
@@ -8480,7 +8480,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>기타 · Ordinary Income BNK</t>
+          <t>기타 · 경상수익</t>
         </is>
       </c>
       <c r="E128" s="20" t="n">
@@ -8514,7 +8514,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>합계 · Ordinary Income BNK</t>
+          <t>합계 · 경상수익</t>
         </is>
       </c>
       <c r="E129" s="20" t="n">
@@ -8548,7 +8548,7 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Ordinary Income BNK</t>
+          <t>조정액 · 경상수익</t>
         </is>
       </c>
       <c r="E130" s="20" t="n">
@@ -8582,7 +8582,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Ordinary Income BNK</t>
+          <t>경상수익</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -8616,7 +8616,7 @@
     <row r="132">
       <c r="A132" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>신금중앙금고 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="E132" s="20" t="n">
@@ -9104,7 +9104,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Allowance For Loan Losses Ope CFBNK</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="E143" s="20" t="n">
@@ -9334,7 +9334,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>Gain On Fund Management Ope CFBNK</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="E148" s="20" t="n">
@@ -9426,7 +9426,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain Related To Securities Ope CFBNK</t>
+          <t>유가증권 관련 손익</t>
         </is>
       </c>
       <c r="E150" s="20" t="n">
@@ -9472,7 +9472,7 @@
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Money Held In Trust Ope CFBNK</t>
+          <t>금전신탁 운용손익</t>
         </is>
       </c>
       <c r="E151" s="20" t="n">
@@ -9610,7 +9610,7 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Trading Assets Ope CFBNK</t>
+          <t>특정거래 자산 순증감</t>
         </is>
       </c>
       <c r="E154" s="20" t="n">
@@ -9656,7 +9656,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Trading Liabilities Ope CFBNK</t>
+          <t>특정거래 부채 순증감</t>
         </is>
       </c>
       <c r="E155" s="20" t="n">
@@ -9702,7 +9702,7 @@
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Trading Accounts Receivable Ope CFBNK</t>
+          <t>특정거래 미수금 순증감</t>
         </is>
       </c>
       <c r="O156" s="20" t="n">
@@ -9718,7 +9718,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Trading Accounts Payable Ope CFBNK</t>
+          <t>특정거래 미지급금 순증감</t>
         </is>
       </c>
       <c r="E157" s="20" t="n">
@@ -9764,7 +9764,7 @@
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Loans And Bills Discounted Ope CFBNK</t>
+          <t>대출금 순증감</t>
         </is>
       </c>
       <c r="E158" s="20" t="n">
@@ -9810,7 +9810,7 @@
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Deposit Ope CFBNK</t>
+          <t>예금 순증감</t>
         </is>
       </c>
       <c r="E159" s="20" t="n">
@@ -9856,7 +9856,7 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Negotiable Certificates Of Deposit Ope CFBNK</t>
+          <t>양도성예금 순증감</t>
         </is>
       </c>
       <c r="O160" s="20" t="n">
@@ -9872,7 +9872,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Debentures Ope CFBNK</t>
+          <t>채권 순증감</t>
         </is>
       </c>
       <c r="E161" s="20" t="n">
@@ -9918,7 +9918,7 @@
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Borrowed Money Excluding Subordinated Borrowings Ope CFBNK</t>
+          <t>차용금(후순위차입금 제외) 순증감</t>
         </is>
       </c>
       <c r="E162" s="20" t="n">
@@ -9964,7 +9964,7 @@
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Deposit Excluding Due From Central Bank Ope CFShinkin BNK</t>
+          <t>예치금(중앙은행 예치금 제외) 순증감</t>
         </is>
       </c>
       <c r="E163" s="20" t="n">
@@ -10010,7 +10010,7 @@
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Call Loans Ope CFBNK</t>
+          <t>콜론 등 순증감</t>
         </is>
       </c>
       <c r="E164" s="20" t="n">
@@ -10056,7 +10056,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Receivables Under Securities Borrowing Transactions Ope CFBNK</t>
+          <t>채권대차거래 지급보증금 순증감</t>
         </is>
       </c>
       <c r="E165" s="20" t="n">
@@ -10102,7 +10102,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Call Money Ope CFBNK</t>
+          <t>콜머니 등 순증감</t>
         </is>
       </c>
       <c r="E166" s="20" t="n">
@@ -10148,7 +10148,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Payables Under Securities Lending Transactions Ope CFBNK</t>
+          <t>채권대차거래 수입담보금 순증감</t>
         </is>
       </c>
       <c r="E167" s="20" t="n">
@@ -10194,7 +10194,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Monetary Claims Bought Ope CFBNK</t>
+          <t>매입금전채권 순증감</t>
         </is>
       </c>
       <c r="E168" s="20" t="n">
@@ -10240,7 +10240,7 @@
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Foreign Exchanges Assets Ope CFBNK</t>
+          <t>외국환(자산) 순증감</t>
         </is>
       </c>
       <c r="E169" s="20" t="n">
@@ -10286,7 +10286,7 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Foreign Exchanges Liabilities Ope CFBNK</t>
+          <t>외국환(부채) 순증감</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
@@ -10332,7 +10332,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Borrowed Money From Trust Account Ope CFBNK</t>
+          <t>신탁계정 차변 순증감</t>
         </is>
       </c>
       <c r="E171" s="20" t="n">
@@ -10378,7 +10378,7 @@
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Fund Management Ope CFBNK</t>
+          <t>자금운용 수입</t>
         </is>
       </c>
       <c r="E172" s="20" t="n">
@@ -10424,7 +10424,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>Payments For Finance Ope CFBNK</t>
+          <t>자금조달 지출</t>
         </is>
       </c>
       <c r="E173" s="20" t="n">
@@ -10792,7 +10792,7 @@
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>Increase In Money Held In Trust Inv CFBNK</t>
+          <t>금전신탁 증가 지출</t>
         </is>
       </c>
       <c r="E181" s="20" t="n">
@@ -10838,7 +10838,7 @@
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>Decrease In Money Held In Trust Inv CFBNK</t>
+          <t>금전신탁 감소 수입</t>
         </is>
       </c>
       <c r="E182" s="20" t="n">
@@ -11081,7 +11081,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>Decrease In Subordinated Borrowings Fin CFBNK</t>
+          <t>후순위차입금 상환 지출</t>
         </is>
       </c>
       <c r="E188" s="20" t="n">
@@ -11115,7 +11115,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Increase Of Shares</t>
+          <t>출자 증액에 따른 수입</t>
         </is>
       </c>
       <c r="E189" s="20" t="n">
@@ -11131,7 +11131,7 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Increase Of Shares Fin CF</t>
+          <t>출자 증액에 따른 수입</t>
         </is>
       </c>
       <c r="E190" s="20" t="n">
@@ -13920,7 +13920,7 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>Cash And Due From Banks</t>
+          <t>현금 및 예치금</t>
         </is>
       </c>
       <c r="C71" s="20" t="n">
@@ -13954,7 +13954,7 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>Call Loans And Bills Bought</t>
+          <t>매입어음 및 콜론</t>
         </is>
       </c>
       <c r="C72" s="20" t="n">
@@ -13988,7 +13988,7 @@
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>Receivables Under Resale Agreements Assets BNK</t>
+          <t>매입현선(RP)계정</t>
         </is>
       </c>
       <c r="C73" s="20" t="n">
@@ -14025,7 +14025,7 @@
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>Receivables Under Securities Borrowing Transactions Assets BNK</t>
+          <t>채권대차거래 지급보증금</t>
         </is>
       </c>
       <c r="C74" s="20" t="n">
@@ -14053,7 +14053,7 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>Monetary Claims Bought Assets BNK</t>
+          <t>매입금전채권</t>
         </is>
       </c>
       <c r="C75" s="20" t="n">
@@ -14090,7 +14090,7 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>Trading Assets Assets BNK</t>
+          <t>특정거래 자산</t>
         </is>
       </c>
       <c r="C76" s="20" t="n">
@@ -14127,7 +14127,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>Derivatives Of Securities Related To Trading Transactions Trading Assets Assets BNK</t>
+          <t>특정거래 유가증권 파생상품</t>
         </is>
       </c>
       <c r="H77" s="20" t="n">
@@ -14137,7 +14137,7 @@
     <row r="78">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>Trading Related Financial Derivatives Trading Assets Assets BNK</t>
+          <t>특정금융 파생상품</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
@@ -14162,7 +14162,7 @@
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>Other Trading Assets Trading Assets Assets BNK</t>
+          <t>기타 특정거래자산</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
@@ -14261,7 +14261,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>Government Bonds Investment Securities Assets BNK</t>
+          <t>국채</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
@@ -14286,7 +14286,7 @@
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>Local Government Bonds Investment Securities Assets BNK</t>
+          <t>지방채</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
@@ -14336,7 +14336,7 @@
     <row r="85">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>Stocks Assets Investment Securities BNK</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
@@ -14361,7 +14361,7 @@
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>Other Securities Investment Securities Assets BNK</t>
+          <t>기타 증권</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
@@ -14386,7 +14386,7 @@
     <row r="87">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>Loans And Bills Discounted Assets BNK</t>
+          <t>대출금</t>
         </is>
       </c>
       <c r="C87" s="20" t="n">
@@ -14423,7 +14423,7 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>Loans On Bills Loans And Bills Discounted Assets BNK</t>
+          <t>어음대출</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
@@ -14448,7 +14448,7 @@
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>Loans On Deeds Loans And Bills Discounted Assets BNK</t>
+          <t>증서대출</t>
         </is>
       </c>
       <c r="F89" s="20" t="n">
@@ -14473,7 +14473,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Overdrafts Loans And Bills Discounted Assets BNK</t>
+          <t>당좌대출</t>
         </is>
       </c>
       <c r="F90" s="20" t="n">
@@ -14498,7 +14498,7 @@
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>Agency Loan Loans And Bills Discounted Assets BNK</t>
+          <t>대리대여금</t>
         </is>
       </c>
       <c r="F91" s="20" t="n">
@@ -14523,7 +14523,7 @@
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>Foreign Exchanges Assets BNK</t>
+          <t>외국환</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
@@ -14560,7 +14560,7 @@
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>Due From Foreign Banks Our Accounts Foreign Exchanges Assets BNK</t>
+          <t>해외 타점 예치금</t>
         </is>
       </c>
       <c r="F93" s="20" t="n">
@@ -14585,7 +14585,7 @@
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>Foreign Bills Bought Foreign Exchanges Assets BNK</t>
+          <t>매입외국환</t>
         </is>
       </c>
       <c r="F94" s="20" t="n">
@@ -14610,7 +14610,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Foreign Bills Receivable Foreign Exchanges Assets BNK</t>
+          <t>추심외국환</t>
         </is>
       </c>
       <c r="F95" s="20" t="n">
@@ -14635,7 +14635,7 @@
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>Other Assets Assets BNK</t>
+          <t>기타 자산</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
@@ -14697,7 +14697,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Accrued Income</t>
+          <t>미수수익</t>
         </is>
       </c>
       <c r="F98" s="20" t="n">
@@ -14722,7 +14722,7 @@
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>Derivatives Other Than For Trading Assets Other Assets BNK</t>
+          <t>금융파생상품</t>
         </is>
       </c>
       <c r="F99" s="20" t="n">
@@ -14747,7 +14747,7 @@
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>Cash Collateral Paid For Financial Instruments Assets</t>
+          <t>금융상품 제공담보금</t>
         </is>
       </c>
       <c r="F100" s="20" t="n">
@@ -14772,7 +14772,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Deposits For Central Counterparty Assets</t>
+          <t>중앙청산기관 차입증거금</t>
         </is>
       </c>
       <c r="H101" s="20" t="n">
@@ -14791,7 +14791,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Other Other Assets Assets BNK</t>
+          <t>기타 자산</t>
         </is>
       </c>
       <c r="D102" s="20" t="n">
@@ -14956,7 +14956,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>Other Net PPE</t>
+          <t>기타 유형자산</t>
         </is>
       </c>
       <c r="F108" s="20" t="n">
@@ -15068,7 +15068,7 @@
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>Other IA</t>
+          <t>기타 무형자산</t>
         </is>
       </c>
       <c r="F112" s="20" t="n">
@@ -15130,7 +15130,7 @@
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Of Obligation Per Contra Assets BNK</t>
+          <t>채무보증 견질</t>
         </is>
       </c>
       <c r="C114" s="20" t="n">
@@ -15204,7 +15204,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>자산 합계</t>
         </is>
       </c>
       <c r="C116" s="12" t="n">
@@ -15241,7 +15241,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Deposits Liabilities BNK</t>
+          <t>예금</t>
         </is>
       </c>
       <c r="C117" s="20" t="n">
@@ -15278,7 +15278,7 @@
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>Current Deposits Deposits Liabilities BNK</t>
+          <t>당좌예금</t>
         </is>
       </c>
       <c r="F118" s="20" t="n">
@@ -15303,7 +15303,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Ordinary Deposits Deposits Liabilities BNK</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="F119" s="20" t="n">
@@ -15328,7 +15328,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Deposits At Notice Deposits Liabilities BNK</t>
+          <t>통지예금</t>
         </is>
       </c>
       <c r="F120" s="20" t="n">
@@ -15353,7 +15353,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Time Deposits Deposits Liabilities BNK</t>
+          <t>정기예금</t>
         </is>
       </c>
       <c r="F121" s="20" t="n">
@@ -15378,7 +15378,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Other Deposits Deposits Liabilities BNK</t>
+          <t>기타 예금</t>
         </is>
       </c>
       <c r="F122" s="20" t="n">
@@ -15403,7 +15403,7 @@
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>Negotiable Certificates Of Deposit Liabilities BNK</t>
+          <t>양도성예금</t>
         </is>
       </c>
       <c r="C123" s="20" t="n">
@@ -15440,7 +15440,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>Debentures Liabilities BNK</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="C124" s="20" t="n">
@@ -15477,7 +15477,7 @@
     <row r="125">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>Debenture Issuance Liabilities BNK</t>
+          <t>채권 발행액</t>
         </is>
       </c>
       <c r="F125" s="20" t="n">
@@ -15502,7 +15502,7 @@
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>Trading Liabilities Liabilities BNK</t>
+          <t>특정거래 부채</t>
         </is>
       </c>
       <c r="C126" s="20" t="n">
@@ -15539,7 +15539,7 @@
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>Trading Related Financial Derivatives Trading Liabilities Liabilities BNK</t>
+          <t>특정금융 파생상품</t>
         </is>
       </c>
       <c r="F127" s="20" t="n">
@@ -15564,7 +15564,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>Borrowed Money Liabilities BNK</t>
+          <t>차용금</t>
         </is>
       </c>
       <c r="C128" s="20" t="n">
@@ -15601,7 +15601,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>Call Money And Bills Sold Shinkin BNK</t>
+          <t>매도어음 및 콜머니</t>
         </is>
       </c>
       <c r="D129" s="20" t="n">
@@ -15648,7 +15648,7 @@
     <row r="131">
       <c r="A131" s="18" t="inlineStr">
         <is>
-          <t>Call Money Liabilities BNK</t>
+          <t>콜머니</t>
         </is>
       </c>
       <c r="D131" s="20" t="n">
@@ -15676,7 +15676,7 @@
     <row r="132">
       <c r="A132" s="18" t="inlineStr">
         <is>
-          <t>Call Money And Bills Sold</t>
+          <t>매도어음 및 콜머니</t>
         </is>
       </c>
       <c r="C132" s="20" t="n">
@@ -15710,7 +15710,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>Payables Under Repurchase Agreements Liabilities BNK</t>
+          <t>매도현선(RP)계정</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
@@ -15747,7 +15747,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>Payables Under Securities Lending Transactions Liabilities BNK</t>
+          <t>채권대차거래 수입담보금</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
@@ -15784,7 +15784,7 @@
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>Foreign Exchanges Liabilities BNK</t>
+          <t>외국환</t>
         </is>
       </c>
       <c r="C135" s="20" t="n">
@@ -15821,7 +15821,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>Due To Foreign Banks Their Accounts Foreign Exchanges Liabilities BNK</t>
+          <t>해외 타점 예수금</t>
         </is>
       </c>
       <c r="F136" s="20" t="n">
@@ -15846,7 +15846,7 @@
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
-          <t>Foreign Bills Sold Foreign Exchanges Liabilities BNK</t>
+          <t>매도외국환</t>
         </is>
       </c>
       <c r="F137" s="20" t="n">
@@ -15871,7 +15871,7 @@
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>Foreign Bills Payable Foreign Exchanges Liabilities BNK</t>
+          <t>미지급 외국환</t>
         </is>
       </c>
       <c r="F138" s="20" t="n">
@@ -15896,7 +15896,7 @@
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>Borrowed Money From Trust Account Liabilities BNK</t>
+          <t>신탁계정 차변</t>
         </is>
       </c>
       <c r="C139" s="20" t="n">
@@ -15933,7 +15933,7 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>Other Liabilities Liabilities BNK</t>
+          <t>기타 부채</t>
         </is>
       </c>
       <c r="C140" s="20" t="n">
@@ -16048,7 +16048,7 @@
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>Variation Margins Of Futures Markets Other Liabilities Liabilities BNK</t>
+          <t>선물거래 차금계정</t>
         </is>
       </c>
       <c r="H144" s="20" t="n">
@@ -16061,7 +16061,7 @@
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>Derivatives Other Than For Trading Liabilities Other Liabilities BNK</t>
+          <t>금융파생상품</t>
         </is>
       </c>
       <c r="F145" s="20" t="n">
@@ -16086,7 +16086,7 @@
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>Cash Collateral Received For Financial Instruments Liabilities</t>
+          <t>금융상품 수입담보금</t>
         </is>
       </c>
       <c r="F146" s="20" t="n">
@@ -16130,7 +16130,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>Other Other Liabilities Liabilities BNK</t>
+          <t>기타 부채</t>
         </is>
       </c>
       <c r="D148" s="20" t="n">
@@ -16334,7 +16334,7 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>Reserves Under The Special Laws2</t>
+          <t>특별법상 충당금</t>
         </is>
       </c>
       <c r="C154" s="20" t="n">
@@ -16445,7 +16445,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Of Obligation Liabilities BNK</t>
+          <t>채무보증</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
@@ -16482,7 +16482,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>부채 합계</t>
         </is>
       </c>
       <c r="C158" s="12" t="n">
@@ -16556,7 +16556,7 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>Common Shares Shinkin BNK</t>
+          <t>보통출자금</t>
         </is>
       </c>
       <c r="F160" s="20" t="n">
@@ -16581,7 +16581,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>Preferred Shares Shinkin BNK</t>
+          <t>우선출자금</t>
         </is>
       </c>
       <c r="F161" s="20" t="n">
@@ -16736,7 +16736,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>Other Retained Earnings</t>
+          <t>기타 이익잉여금</t>
         </is>
       </c>
       <c r="D166" s="20" t="n">
@@ -16764,7 +16764,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>Special Reserve Shinkin BNK</t>
+          <t>특별적립금</t>
         </is>
       </c>
       <c r="D167" s="20" t="n">
@@ -16842,7 +16842,7 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>Promotion Fund Shinkin BNK</t>
+          <t>진흥기금</t>
         </is>
       </c>
       <c r="D170" s="20" t="n">
@@ -16870,7 +16870,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>Unappropriated Retained Earnings Shinkin BNK</t>
+          <t>당기 미처분 잉여금</t>
         </is>
       </c>
       <c r="D171" s="20" t="n">
@@ -16898,7 +16898,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>Shareholders Equity Shinkin BNK</t>
+          <t>회원 계정 합계</t>
         </is>
       </c>
       <c r="C172" s="12" t="n">
@@ -17194,7 +17194,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>Net Assets</t>
+          <t>순자산 합계</t>
         </is>
       </c>
       <c r="C180" s="12" t="n">
@@ -17231,7 +17231,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>Liabilities And Net Assets</t>
+          <t>부채 및 순자산 합계</t>
         </is>
       </c>
       <c r="C181" s="12" t="n">
@@ -17268,7 +17268,7 @@
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>Cash And Due From Banks Shinkin BNK</t>
+          <t>현금 및 예치금</t>
         </is>
       </c>
       <c r="D182" s="20" t="n">
@@ -17290,7 +17290,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>Call Loans And Bills Bought Shinkin BNK</t>
+          <t>매입어음 및 콜론</t>
         </is>
       </c>
       <c r="D183" s="20" t="n">
@@ -17312,7 +17312,7 @@
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>Cash Assets BNK</t>
+          <t>현금</t>
         </is>
       </c>
       <c r="D184" s="20" t="n">
@@ -17368,7 +17368,7 @@
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>Call Loans Assets BNK</t>
+          <t>콜론</t>
         </is>
       </c>
       <c r="D186" s="20" t="n">

--- a/docs/data/jp/xlsx/8421.xlsx
+++ b/docs/data/jp/xlsx/8421.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -705,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC195"/>
+  <dimension ref="A1:AC204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4375,10 +4378,12 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>187800</v>
+      </c>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="29" t="n"/>
       <c r="E50" s="29" t="n"/>
@@ -4413,7 +4418,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B51" s="27" t="n"/>
+      <c r="B51" s="27" t="n">
+        <v>8708222</v>
+      </c>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="29" t="n"/>
       <c r="E51" s="29" t="n"/>
@@ -5612,7 +5619,7 @@
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C77" s="39" t="n"/>
@@ -5864,5516 +5871,5972 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
-        <is>
-          <t>자금운용수익</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="n">
-        <v>55218</v>
-      </c>
-      <c r="D82" s="20" t="n">
-        <v>94463</v>
-      </c>
-      <c r="E82" s="20" t="n">
-        <v>74424</v>
-      </c>
-      <c r="F82" s="20" t="n">
-        <v>89798</v>
-      </c>
-      <c r="G82" s="20" t="n">
-        <v>86238</v>
-      </c>
-      <c r="H82" s="20" t="n">
-        <v>109263</v>
-      </c>
-      <c r="I82" s="20" t="n">
-        <v>114520</v>
-      </c>
-      <c r="J82" s="20" t="n">
-        <v>127990</v>
-      </c>
-      <c r="K82" s="20" t="n">
-        <v>143076</v>
-      </c>
-      <c r="L82" s="20" t="n">
-        <v>144569</v>
-      </c>
-      <c r="M82" s="20" t="n">
-        <v>155053</v>
-      </c>
-      <c r="N82" s="20" t="n">
-        <v>168217</v>
-      </c>
-      <c r="T82" s="20" t="n">
-        <v>42180</v>
-      </c>
-      <c r="U82" s="20" t="n">
-        <v>58073</v>
-      </c>
-      <c r="V82" s="20" t="n">
-        <v>74424</v>
-      </c>
-      <c r="W82" s="20" t="n">
-        <v>114520</v>
-      </c>
-      <c r="X82" s="20" t="n">
-        <v>155053</v>
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="15">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="15">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="15">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="15">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="15">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="15">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="15">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="15">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="15">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="15">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="15">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="15">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="15">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>(이 중 대출금 이자)</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="C83" s="20" t="n">
-        <v>5756</v>
+        <v>55218</v>
       </c>
       <c r="D83" s="20" t="n">
-        <v>6029</v>
+        <v>94463</v>
       </c>
       <c r="E83" s="20" t="n">
-        <v>6407</v>
+        <v>74424</v>
       </c>
       <c r="F83" s="20" t="n">
-        <v>7449</v>
+        <v>89798</v>
       </c>
       <c r="G83" s="20" t="n">
-        <v>8740</v>
+        <v>86238</v>
       </c>
       <c r="H83" s="20" t="n">
-        <v>10755</v>
+        <v>109263</v>
       </c>
       <c r="I83" s="20" t="n">
-        <v>12901</v>
+        <v>114520</v>
       </c>
       <c r="J83" s="20" t="n">
-        <v>15984</v>
+        <v>127990</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>16784</v>
+        <v>143076</v>
       </c>
       <c r="L83" s="20" t="n">
-        <v>19565</v>
+        <v>144569</v>
       </c>
       <c r="M83" s="20" t="n">
-        <v>26087</v>
+        <v>155053</v>
       </c>
       <c r="N83" s="20" t="n">
-        <v>33741</v>
+        <v>168217</v>
       </c>
       <c r="T83" s="20" t="n">
-        <v>3955</v>
+        <v>42180</v>
       </c>
       <c r="U83" s="20" t="n">
-        <v>5347</v>
+        <v>58073</v>
       </c>
       <c r="V83" s="20" t="n">
-        <v>6407</v>
+        <v>74424</v>
       </c>
       <c r="W83" s="20" t="n">
-        <v>12901</v>
+        <v>114520</v>
       </c>
       <c r="X83" s="20" t="n">
-        <v>26087</v>
+        <v>155053</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>(이 중 유가증권 이자·배당금)</t>
+          <t>(이 중 대출금 이자)</t>
         </is>
       </c>
       <c r="C84" s="20" t="n">
-        <v>46213</v>
+        <v>5756</v>
       </c>
       <c r="D84" s="20" t="n">
-        <v>84990</v>
+        <v>6029</v>
       </c>
       <c r="E84" s="20" t="n">
-        <v>63507</v>
+        <v>6407</v>
       </c>
       <c r="F84" s="20" t="n">
-        <v>74957</v>
+        <v>7449</v>
       </c>
       <c r="G84" s="20" t="n">
-        <v>65318</v>
+        <v>8740</v>
       </c>
       <c r="H84" s="20" t="n">
-        <v>83644</v>
+        <v>10755</v>
       </c>
       <c r="I84" s="20" t="n">
-        <v>80574</v>
+        <v>12901</v>
       </c>
       <c r="J84" s="20" t="n">
-        <v>88489</v>
+        <v>15984</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>103285</v>
+        <v>16784</v>
       </c>
       <c r="L84" s="20" t="n">
-        <v>101556</v>
+        <v>19565</v>
       </c>
       <c r="M84" s="20" t="n">
-        <v>101669</v>
+        <v>26087</v>
       </c>
       <c r="N84" s="20" t="n">
-        <v>109859</v>
+        <v>33741</v>
       </c>
       <c r="T84" s="20" t="n">
-        <v>36246</v>
+        <v>3955</v>
       </c>
       <c r="U84" s="20" t="n">
-        <v>49492</v>
+        <v>5347</v>
       </c>
       <c r="V84" s="20" t="n">
-        <v>63507</v>
+        <v>6407</v>
       </c>
       <c r="W84" s="20" t="n">
-        <v>80574</v>
+        <v>12901</v>
       </c>
       <c r="X84" s="20" t="n">
-        <v>101669</v>
+        <v>26087</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>신탁보수</t>
+          <t>(이 중 유가증권 이자·배당금)</t>
         </is>
       </c>
       <c r="C85" s="20" t="n">
-        <v>635</v>
+        <v>46213</v>
       </c>
       <c r="D85" s="20" t="n">
-        <v>639</v>
+        <v>84990</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>635</v>
+        <v>63507</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>639</v>
+        <v>74957</v>
       </c>
       <c r="G85" s="20" t="n">
-        <v>652</v>
+        <v>65318</v>
       </c>
       <c r="H85" s="20" t="n">
-        <v>652</v>
+        <v>83644</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>638</v>
+        <v>80574</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>642</v>
+        <v>88489</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>649</v>
+        <v>103285</v>
       </c>
       <c r="L85" s="20" t="n">
-        <v>623</v>
+        <v>101556</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>579</v>
+        <v>101669</v>
       </c>
       <c r="N85" s="20" t="n">
-        <v>543</v>
+        <v>109859</v>
       </c>
       <c r="T85" s="20" t="n">
-        <v>540</v>
+        <v>36246</v>
       </c>
       <c r="U85" s="20" t="n">
-        <v>608</v>
+        <v>49492</v>
       </c>
       <c r="V85" s="20" t="n">
-        <v>635</v>
+        <v>63507</v>
       </c>
       <c r="W85" s="20" t="n">
-        <v>638</v>
+        <v>80574</v>
       </c>
       <c r="X85" s="20" t="n">
-        <v>579</v>
+        <v>101669</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>용역거래 수익</t>
+          <t>신탁보수</t>
         </is>
       </c>
       <c r="C86" s="20" t="n">
-        <v>-5852</v>
+        <v>635</v>
       </c>
       <c r="D86" s="20" t="n">
-        <v>27767</v>
+        <v>639</v>
       </c>
       <c r="E86" s="20" t="n">
-        <v>-22650</v>
+        <v>635</v>
       </c>
       <c r="F86" s="20" t="n">
-        <v>11288</v>
+        <v>639</v>
       </c>
       <c r="G86" s="20" t="n">
-        <v>-5951</v>
+        <v>652</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>28924</v>
+        <v>652</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>11787</v>
+        <v>638</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>11752</v>
+        <v>642</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>-5813</v>
+        <v>649</v>
       </c>
       <c r="L86" s="20" t="n">
-        <v>30267</v>
+        <v>623</v>
       </c>
       <c r="M86" s="20" t="n">
-        <v>12620</v>
+        <v>579</v>
       </c>
       <c r="N86" s="20" t="n">
-        <v>12793</v>
+        <v>543</v>
       </c>
       <c r="T86" s="20" t="n">
-        <v>-22402</v>
+        <v>540</v>
       </c>
       <c r="U86" s="20" t="n">
-        <v>10765</v>
+        <v>608</v>
       </c>
       <c r="V86" s="20" t="n">
-        <v>-22650</v>
+        <v>635</v>
       </c>
       <c r="W86" s="20" t="n">
-        <v>11787</v>
+        <v>638</v>
       </c>
       <c r="X86" s="20" t="n">
-        <v>12620</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>특정거래 수익</t>
+          <t>용역거래 수익</t>
         </is>
       </c>
       <c r="C87" s="20" t="n">
-        <v>6989</v>
+        <v>-5852</v>
       </c>
       <c r="D87" s="20" t="n">
-        <v>4819</v>
+        <v>27767</v>
       </c>
       <c r="E87" s="20" t="n">
-        <v>2682</v>
+        <v>-22650</v>
       </c>
       <c r="F87" s="20" t="n">
-        <v>6509</v>
+        <v>11288</v>
       </c>
       <c r="G87" s="20" t="n">
-        <v>1694</v>
+        <v>-5951</v>
       </c>
       <c r="H87" s="20" t="n">
-        <v>2258</v>
+        <v>28924</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>1960</v>
+        <v>11787</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>1030</v>
+        <v>11752</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>977</v>
+        <v>-5813</v>
       </c>
       <c r="L87" s="20" t="n">
-        <v>1182</v>
+        <v>30267</v>
       </c>
       <c r="M87" s="20" t="n">
-        <v>1335</v>
+        <v>12620</v>
       </c>
       <c r="N87" s="20" t="n">
-        <v>1086</v>
+        <v>12793</v>
       </c>
       <c r="T87" s="20" t="n">
-        <v>-50</v>
+        <v>-22402</v>
       </c>
       <c r="U87" s="20" t="n">
-        <v>2537</v>
+        <v>10765</v>
       </c>
       <c r="V87" s="20" t="n">
-        <v>2682</v>
+        <v>-22650</v>
       </c>
       <c r="W87" s="20" t="n">
-        <v>1960</v>
+        <v>11787</v>
       </c>
       <c r="X87" s="20" t="n">
-        <v>1335</v>
+        <v>12620</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>기타 업무수익</t>
+          <t>특정거래 수익</t>
         </is>
       </c>
       <c r="C88" s="20" t="n">
-        <v>18758</v>
+        <v>6989</v>
       </c>
       <c r="D88" s="20" t="n">
-        <v>5834</v>
+        <v>4819</v>
       </c>
       <c r="E88" s="20" t="n">
-        <v>10332</v>
+        <v>2682</v>
       </c>
       <c r="F88" s="20" t="n">
-        <v>2568</v>
+        <v>6509</v>
       </c>
       <c r="G88" s="20" t="n">
-        <v>5583</v>
+        <v>1694</v>
       </c>
       <c r="H88" s="20" t="n">
-        <v>1203</v>
+        <v>2258</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>8375</v>
+        <v>1960</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>9081</v>
+        <v>1030</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>9811</v>
+        <v>977</v>
       </c>
       <c r="L88" s="20" t="n">
-        <v>8915</v>
+        <v>1182</v>
       </c>
       <c r="M88" s="20" t="n">
-        <v>5477</v>
+        <v>1335</v>
       </c>
       <c r="N88" s="20" t="n">
-        <v>9934</v>
+        <v>1086</v>
       </c>
       <c r="T88" s="20" t="n">
-        <v>1971</v>
+        <v>-50</v>
       </c>
       <c r="U88" s="20" t="n">
-        <v>35896</v>
+        <v>2537</v>
       </c>
       <c r="V88" s="20" t="n">
-        <v>10332</v>
+        <v>2682</v>
       </c>
       <c r="W88" s="20" t="n">
-        <v>8375</v>
+        <v>1960</v>
       </c>
       <c r="X88" s="20" t="n">
-        <v>5477</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>기타 경상수익</t>
+          <t>기타 업무수익</t>
         </is>
       </c>
       <c r="C89" s="20" t="n">
-        <v>338</v>
+        <v>18758</v>
       </c>
       <c r="D89" s="20" t="n">
-        <v>1408</v>
+        <v>5834</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>20607</v>
+        <v>10332</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>564</v>
+        <v>2568</v>
       </c>
       <c r="G89" s="20" t="n">
-        <v>2590</v>
+        <v>5583</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>144</v>
+        <v>1203</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>685</v>
+        <v>8375</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>0</v>
+        <v>9081</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>2823</v>
+        <v>9811</v>
       </c>
       <c r="L89" s="20" t="n">
-        <v>-50</v>
+        <v>8915</v>
       </c>
       <c r="M89" s="20" t="n">
-        <v>32</v>
+        <v>5477</v>
       </c>
       <c r="N89" s="20" t="n">
-        <v>505</v>
+        <v>9934</v>
       </c>
       <c r="T89" s="20" t="n">
-        <v>319</v>
+        <v>1971</v>
       </c>
       <c r="U89" s="20" t="n">
-        <v>5992</v>
+        <v>35896</v>
       </c>
       <c r="V89" s="20" t="n">
-        <v>20607</v>
+        <v>10332</v>
       </c>
       <c r="W89" s="20" t="n">
-        <v>685</v>
+        <v>8375</v>
       </c>
       <c r="X89" s="20" t="n">
-        <v>32</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>경상비용</t>
+          <t>기타 경상수익</t>
         </is>
       </c>
       <c r="C90" s="20" t="n">
-        <v>66481</v>
+        <v>338</v>
       </c>
       <c r="D90" s="20" t="n">
-        <v>126141</v>
+        <v>1408</v>
       </c>
       <c r="E90" s="20" t="n">
-        <v>74539</v>
+        <v>20607</v>
       </c>
       <c r="F90" s="20" t="n">
-        <v>92211</v>
+        <v>564</v>
       </c>
       <c r="G90" s="20" t="n">
-        <v>82456</v>
+        <v>2590</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>123279</v>
+        <v>144</v>
       </c>
       <c r="I90" s="20" t="n">
-        <v>126052</v>
+        <v>685</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>135951</v>
+        <v>0</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>129597</v>
+        <v>2823</v>
       </c>
       <c r="L90" s="20" t="n">
-        <v>174201</v>
+        <v>-50</v>
       </c>
       <c r="M90" s="20" t="n">
-        <v>166718</v>
+        <v>32</v>
       </c>
       <c r="N90" s="20" t="n">
-        <v>174545</v>
+        <v>505</v>
       </c>
       <c r="T90" s="20" t="n">
-        <v>19443</v>
+        <v>319</v>
       </c>
       <c r="U90" s="20" t="n">
-        <v>116122</v>
+        <v>5992</v>
       </c>
       <c r="V90" s="20" t="n">
-        <v>74539</v>
+        <v>20607</v>
       </c>
       <c r="W90" s="20" t="n">
-        <v>126052</v>
+        <v>685</v>
       </c>
       <c r="X90" s="20" t="n">
-        <v>166718</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>자금조달비용</t>
+          <t>경상비용</t>
         </is>
       </c>
       <c r="C91" s="20" t="n">
-        <v>40359</v>
+        <v>66481</v>
       </c>
       <c r="D91" s="20" t="n">
-        <v>46371</v>
+        <v>126141</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>55770</v>
+        <v>74539</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>68402</v>
+        <v>92211</v>
       </c>
       <c r="G91" s="20" t="n">
-        <v>73981</v>
+        <v>82456</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>83057</v>
+        <v>123279</v>
       </c>
       <c r="I91" s="20" t="n">
-        <v>93251</v>
+        <v>126052</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>102719</v>
+        <v>135951</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>113459</v>
+        <v>129597</v>
       </c>
       <c r="L91" s="20" t="n">
-        <v>120912</v>
+        <v>174201</v>
       </c>
       <c r="M91" s="20" t="n">
-        <v>127604</v>
+        <v>166718</v>
       </c>
       <c r="N91" s="20" t="n">
-        <v>133491</v>
+        <v>174545</v>
       </c>
       <c r="T91" s="20" t="n">
-        <v>17125</v>
+        <v>19443</v>
       </c>
       <c r="U91" s="20" t="n">
-        <v>32923</v>
+        <v>116122</v>
       </c>
       <c r="V91" s="20" t="n">
-        <v>55770</v>
+        <v>74539</v>
       </c>
       <c r="W91" s="20" t="n">
-        <v>93251</v>
+        <v>126052</v>
       </c>
       <c r="X91" s="20" t="n">
-        <v>127604</v>
+        <v>166718</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>(이 중 예금 이자)</t>
+          <t>자금조달비용</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
-        <v>11831</v>
+        <v>40359</v>
       </c>
       <c r="D92" s="20" t="n">
-        <v>10980</v>
+        <v>46371</v>
       </c>
       <c r="E92" s="20" t="n">
-        <v>9603</v>
+        <v>55770</v>
       </c>
       <c r="F92" s="20" t="n">
-        <v>14581</v>
+        <v>68402</v>
       </c>
       <c r="G92" s="20" t="n">
-        <v>17356</v>
+        <v>73981</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>20644</v>
+        <v>83057</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>27469</v>
+        <v>93251</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>33252</v>
+        <v>102719</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>37196</v>
+        <v>113459</v>
       </c>
       <c r="L92" s="20" t="n">
-        <v>39631</v>
+        <v>120912</v>
       </c>
       <c r="M92" s="20" t="n">
-        <v>46636</v>
+        <v>127604</v>
       </c>
       <c r="N92" s="20" t="n">
-        <v>52375</v>
+        <v>133491</v>
       </c>
       <c r="T92" s="20" t="n">
-        <v>7235</v>
+        <v>17125</v>
       </c>
       <c r="U92" s="20" t="n">
-        <v>11308</v>
+        <v>32923</v>
       </c>
       <c r="V92" s="20" t="n">
-        <v>9603</v>
+        <v>55770</v>
       </c>
       <c r="W92" s="20" t="n">
-        <v>27469</v>
+        <v>93251</v>
       </c>
       <c r="X92" s="20" t="n">
-        <v>46636</v>
+        <v>127604</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>(이 중 채권이자)</t>
+          <t>(이 중 예금 이자)</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
-        <v>364</v>
+        <v>11831</v>
       </c>
       <c r="D93" s="20" t="n">
-        <v>399</v>
+        <v>10980</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>451</v>
+        <v>9603</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>509</v>
+        <v>14581</v>
       </c>
       <c r="G93" s="20" t="n">
-        <v>637</v>
+        <v>17356</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>716</v>
+        <v>20644</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>835</v>
+        <v>27469</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>1009</v>
+        <v>33252</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>1204</v>
+        <v>37196</v>
       </c>
       <c r="L93" s="20" t="n">
-        <v>1358</v>
+        <v>39631</v>
       </c>
       <c r="M93" s="20" t="n">
-        <v>1551</v>
+        <v>46636</v>
       </c>
       <c r="N93" s="20" t="n">
-        <v>1840</v>
+        <v>52375</v>
       </c>
       <c r="T93" s="20" t="n">
-        <v>283</v>
+        <v>7235</v>
       </c>
       <c r="U93" s="20" t="n">
-        <v>312</v>
+        <v>11308</v>
       </c>
       <c r="V93" s="20" t="n">
-        <v>451</v>
+        <v>9603</v>
       </c>
       <c r="W93" s="20" t="n">
-        <v>835</v>
+        <v>27469</v>
       </c>
       <c r="X93" s="20" t="n">
-        <v>1551</v>
+        <v>46636</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>용역거래 비용</t>
+          <t>(이 중 채권이자)</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
-        <v>578</v>
+        <v>364</v>
       </c>
       <c r="D94" s="20" t="n">
-        <v>7178</v>
+        <v>399</v>
       </c>
       <c r="E94" s="20" t="n">
-        <v>-2702</v>
+        <v>451</v>
       </c>
       <c r="F94" s="20" t="n">
-        <v>4049</v>
+        <v>509</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>861</v>
+        <v>637</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>7642</v>
+        <v>716</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>4067</v>
+        <v>835</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>4152</v>
+        <v>1009</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>899</v>
+        <v>1204</v>
       </c>
       <c r="L94" s="20" t="n">
-        <v>7722</v>
+        <v>1358</v>
       </c>
       <c r="M94" s="20" t="n">
-        <v>4576</v>
+        <v>1551</v>
       </c>
       <c r="N94" s="20" t="n">
-        <v>5023</v>
+        <v>1840</v>
       </c>
       <c r="T94" s="20" t="n">
-        <v>-3362</v>
+        <v>283</v>
       </c>
       <c r="U94" s="20" t="n">
-        <v>3675</v>
+        <v>312</v>
       </c>
       <c r="V94" s="20" t="n">
-        <v>-2702</v>
+        <v>451</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>4067</v>
+        <v>835</v>
       </c>
       <c r="X94" s="20" t="n">
-        <v>4576</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>특정거래 비용</t>
+          <t>용역거래 비용</t>
         </is>
       </c>
       <c r="C95" s="20" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="D95" s="20" t="n">
-        <v>0</v>
+        <v>7178</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0</v>
+        <v>-2702</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>1</v>
+        <v>4049</v>
       </c>
       <c r="G95" s="20" t="n">
-        <v>-1</v>
+        <v>861</v>
       </c>
       <c r="H95" s="20" t="n">
-        <v>0</v>
+        <v>7642</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>0</v>
+        <v>4067</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>16</v>
+        <v>899</v>
       </c>
       <c r="L95" s="20" t="n">
-        <v>53</v>
+        <v>7722</v>
       </c>
       <c r="M95" s="20" t="n">
-        <v>47</v>
+        <v>4576</v>
       </c>
       <c r="N95" s="20" t="n">
-        <v>119</v>
+        <v>5023</v>
       </c>
       <c r="T95" s="20" t="n">
-        <v>-16</v>
+        <v>-3362</v>
       </c>
       <c r="U95" s="20" t="n">
-        <v>-68</v>
+        <v>3675</v>
       </c>
       <c r="V95" s="20" t="n">
-        <v>0</v>
+        <v>-2702</v>
       </c>
       <c r="W95" s="20" t="n">
-        <v>0</v>
+        <v>4067</v>
       </c>
       <c r="X95" s="20" t="n">
-        <v>47</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>기타 업무비용</t>
+          <t>특정거래 비용</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
-        <v>23882</v>
+        <v>0</v>
       </c>
       <c r="D96" s="20" t="n">
-        <v>45491</v>
+        <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>31363</v>
+        <v>0</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>5016</v>
+        <v>1</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>5534</v>
+        <v>-1</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>5702</v>
+        <v>0</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>11948</v>
+        <v>0</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>13206</v>
+        <v>0</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>13124</v>
+        <v>16</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>16238</v>
+        <v>53</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>17497</v>
+        <v>47</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>19823</v>
+        <v>119</v>
       </c>
       <c r="T96" s="20" t="n">
-        <v>14154</v>
+        <v>-16</v>
       </c>
       <c r="U96" s="20" t="n">
-        <v>63197</v>
+        <v>-68</v>
       </c>
       <c r="V96" s="20" t="n">
-        <v>31363</v>
+        <v>0</v>
       </c>
       <c r="W96" s="20" t="n">
-        <v>11948</v>
+        <v>0</v>
       </c>
       <c r="X96" s="20" t="n">
-        <v>17497</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>경비</t>
-        </is>
+          <t>기타 업무비용</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="n">
+        <v>23882</v>
+      </c>
+      <c r="D97" s="20" t="n">
+        <v>45491</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>-9892</v>
+        <v>31363</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>14736</v>
+        <v>5016</v>
+      </c>
+      <c r="G97" s="20" t="n">
+        <v>5534</v>
+      </c>
+      <c r="H97" s="20" t="n">
+        <v>5702</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>16801</v>
+        <v>11948</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>15650</v>
+        <v>13206</v>
+      </c>
+      <c r="K97" s="20" t="n">
+        <v>13124</v>
+      </c>
+      <c r="L97" s="20" t="n">
+        <v>16238</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>16563</v>
+        <v>17497</v>
       </c>
       <c r="N97" s="20" t="n">
-        <v>15896</v>
+        <v>19823</v>
       </c>
       <c r="T97" s="20" t="n">
-        <v>-8791</v>
+        <v>14154</v>
       </c>
       <c r="U97" s="20" t="n">
-        <v>16452</v>
+        <v>63197</v>
       </c>
       <c r="V97" s="20" t="n">
-        <v>-9892</v>
+        <v>31363</v>
       </c>
       <c r="W97" s="20" t="n">
-        <v>16801</v>
+        <v>11948</v>
       </c>
       <c r="X97" s="20" t="n">
-        <v>16563</v>
+        <v>17497</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="n">
+        <v>-9892</v>
+      </c>
+      <c r="F98" s="20" t="n">
+        <v>14736</v>
+      </c>
+      <c r="I98" s="20" t="n">
+        <v>16801</v>
+      </c>
+      <c r="J98" s="20" t="n">
+        <v>15650</v>
+      </c>
+      <c r="M98" s="20" t="n">
+        <v>16563</v>
+      </c>
+      <c r="N98" s="20" t="n">
+        <v>15896</v>
+      </c>
+      <c r="T98" s="20" t="n">
+        <v>-8791</v>
+      </c>
+      <c r="U98" s="20" t="n">
+        <v>16452</v>
+      </c>
+      <c r="V98" s="20" t="n">
+        <v>-9892</v>
+      </c>
+      <c r="W98" s="20" t="n">
+        <v>16801</v>
+      </c>
+      <c r="X98" s="20" t="n">
+        <v>16563</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
           <t>기타 경상비용</t>
         </is>
       </c>
-      <c r="C98" s="20" t="n">
+      <c r="C99" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="20" t="n">
+      <c r="D99" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="20" t="n">
+      <c r="E99" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F98" s="20" t="n">
+      <c r="F99" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G98" s="20" t="n">
+      <c r="G99" s="20" t="n">
         <v>81</v>
       </c>
-      <c r="H98" s="20" t="n">
+      <c r="H99" s="20" t="n">
         <v>51</v>
       </c>
-      <c r="I98" s="20" t="n">
+      <c r="I99" s="20" t="n">
         <v>-14</v>
       </c>
-      <c r="J98" s="20" t="n">
+      <c r="J99" s="20" t="n">
         <v>222</v>
       </c>
-      <c r="K98" s="20" t="n">
+      <c r="K99" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="L98" s="20" t="n">
+      <c r="L99" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="M98" s="20" t="n">
+      <c r="M99" s="20" t="n">
         <v>430</v>
       </c>
-      <c r="N98" s="20" t="n">
+      <c r="N99" s="20" t="n">
         <v>191</v>
       </c>
-      <c r="T98" s="20" t="n">
+      <c r="T99" s="20" t="n">
         <v>334</v>
       </c>
-      <c r="U98" s="20" t="n">
+      <c r="U99" s="20" t="n">
         <v>-55</v>
       </c>
-      <c r="V98" s="20" t="n">
+      <c r="V99" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="20" t="n">
+      <c r="W99" s="20" t="n">
         <v>-14</v>
       </c>
-      <c r="X98" s="20" t="n">
+      <c r="X99" s="20" t="n">
         <v>430</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>경상이익</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C100" s="12" t="n">
         <v>9606</v>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D100" s="12" t="n">
         <v>8788</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E100" s="12" t="n">
         <v>11491</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F100" s="12" t="n">
         <v>19157</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>8350</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>19165</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I100" s="12" t="n">
         <v>11913</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J100" s="12" t="n">
         <v>14546</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>21927</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>11304</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="M100" s="12" t="n">
         <v>8379</v>
       </c>
-      <c r="N99" s="12" t="n">
+      <c r="N100" s="12" t="n">
         <v>18535</v>
       </c>
-      <c r="T99" s="12" t="n">
+      <c r="T100" s="12" t="n">
         <v>3113</v>
       </c>
-      <c r="U99" s="12" t="n">
+      <c r="U100" s="12" t="n">
         <v>-2251</v>
       </c>
-      <c r="V99" s="12" t="n">
+      <c r="V100" s="12" t="n">
         <v>11491</v>
       </c>
-      <c r="W99" s="12" t="n">
+      <c r="W100" s="12" t="n">
         <v>11913</v>
       </c>
-      <c r="X99" s="12" t="n">
+      <c r="X100" s="12" t="n">
         <v>8379</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="18" t="inlineStr">
-        <is>
-          <t>특별이익</t>
-        </is>
-      </c>
-      <c r="C100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="20" t="n">
-        <v>3764</v>
-      </c>
-      <c r="N100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="U100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="20" t="n">
-        <v>3764</v>
-      </c>
-    </row>
     <row r="101">
-      <c r="A101" s="18" t="inlineStr">
-        <is>
-          <t>고정자산 처분이익</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="U101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="20" t="n">
-        <v>0</v>
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G101" s="15">
+        <f>IF(OR(G100="",C100=""),"",IF(C100&lt;=0,"",IFERROR(G100/C100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H101" s="15">
+        <f>IF(OR(H100="",D100=""),"",IF(D100&lt;=0,"",IFERROR(H100/D100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I101" s="15">
+        <f>IF(OR(I100="",E100=""),"",IF(E100&lt;=0,"",IFERROR(I100/E100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J101" s="15">
+        <f>IF(OR(J100="",F100=""),"",IF(F100&lt;=0,"",IFERROR(J100/F100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K101" s="15">
+        <f>IF(OR(K100="",G100=""),"",IF(G100&lt;=0,"",IFERROR(K100/G100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L101" s="15">
+        <f>IF(OR(L100="",H100=""),"",IF(H100&lt;=0,"",IFERROR(L100/H100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M101" s="15">
+        <f>IF(OR(M100="",I100=""),"",IF(I100&lt;=0,"",IFERROR(M100/I100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N101" s="15">
+        <f>IF(OR(N100="",J100=""),"",IF(J100&lt;=0,"",IFERROR(N100/J100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T101" s="15">
+        <f>IF(OR(T100="",S100=""),"",IF(S100&lt;=0,"",IFERROR(T100/S100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U101" s="15">
+        <f>IF(OR(U100="",T100=""),"",IF(T100&lt;=0,"",IFERROR(U100/T100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V101" s="15">
+        <f>IF(OR(V100="",U100=""),"",IF(U100&lt;=0,"",IFERROR(V100/U100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W101" s="15">
+        <f>IF(OR(W100="",V100=""),"",IF(V100&lt;=0,"",IFERROR(W100/V100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X101" s="15">
+        <f>IF(OR(X100="",W100=""),"",IF(W100&lt;=0,"",IFERROR(X100/W100-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>특별손실</t>
+          <t>특별이익</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D102" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F102" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="L102" s="20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M102" s="20" t="n">
-        <v>351</v>
+        <v>3764</v>
       </c>
       <c r="N102" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T102" s="20" t="n">
-        <v>-3</v>
+        <v>54</v>
       </c>
       <c r="U102" s="20" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="V102" s="20" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="W102" s="20" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="X102" s="20" t="n">
-        <v>351</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>고정자산 처분손실</t>
-        </is>
-      </c>
-      <c r="C103" s="20" t="n">
-        <v>2</v>
+          <t>고정자산 처분이익</t>
+        </is>
       </c>
       <c r="D103" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="F103" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H103" s="20" t="n">
-        <v>187</v>
-      </c>
-      <c r="I103" s="20" t="n">
-        <v>82</v>
-      </c>
-      <c r="J103" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K103" s="20" t="n">
-        <v>379</v>
-      </c>
-      <c r="L103" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M103" s="20" t="n">
-        <v>347</v>
-      </c>
-      <c r="N103" s="20" t="n">
+      <c r="T103" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="U103" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U103" s="20" t="n">
-        <v>76</v>
-      </c>
       <c r="V103" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="W103" s="20" t="n">
-        <v>82</v>
-      </c>
-      <c r="X103" s="20" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>금융상품거래 책임준비금 전입액</t>
+          <t>특별손실</t>
         </is>
       </c>
       <c r="C104" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104" s="20" t="n">
         <v>3</v>
       </c>
       <c r="E104" s="20" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="F104" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="20" t="n">
-        <v>2</v>
+        <v>194</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>3</v>
+        <v>378</v>
       </c>
       <c r="L104" s="20" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M104" s="20" t="n">
-        <v>5</v>
+        <v>351</v>
       </c>
       <c r="N104" s="20" t="n">
         <v>3</v>
       </c>
       <c r="T104" s="20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U104" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="V104" s="20" t="n">
+        <v>137</v>
+      </c>
+      <c r="W104" s="20" t="n">
+        <v>83</v>
+      </c>
+      <c r="X104" s="20" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>고정자산 처분손실</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="U104" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V104" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W104" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X104" s="20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>9604</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>8785</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>11353</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>19155</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>8350</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>18972</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>11830</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>14536</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>21550</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>11293</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>11792</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>18532</v>
-      </c>
-      <c r="T105" s="12" t="n">
-        <v>3172</v>
-      </c>
-      <c r="U105" s="12" t="n">
-        <v>-2382</v>
-      </c>
-      <c r="V105" s="12" t="n">
-        <v>11353</v>
-      </c>
-      <c r="W105" s="12" t="n">
-        <v>11830</v>
-      </c>
-      <c r="X105" s="12" t="n">
-        <v>11792</v>
+      <c r="E105" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="F105" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" s="20" t="n">
+        <v>187</v>
+      </c>
+      <c r="I105" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="J105" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K105" s="20" t="n">
+        <v>379</v>
+      </c>
+      <c r="L105" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M105" s="20" t="n">
+        <v>347</v>
+      </c>
+      <c r="N105" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U105" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="V105" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="W105" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="X105" s="20" t="n">
+        <v>347</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>금융상품거래 책임준비금 전입액</t>
         </is>
       </c>
       <c r="C106" s="20" t="n">
-        <v>3044</v>
+        <v>0</v>
       </c>
       <c r="D106" s="20" t="n">
-        <v>2192</v>
+        <v>3</v>
       </c>
       <c r="E106" s="20" t="n">
-        <v>3506</v>
+        <v>1</v>
       </c>
       <c r="F106" s="20" t="n">
-        <v>4491</v>
+        <v>1</v>
       </c>
       <c r="G106" s="20" t="n">
-        <v>2742</v>
+        <v>1</v>
       </c>
       <c r="H106" s="20" t="n">
-        <v>5139</v>
+        <v>2</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>3411</v>
+        <v>2</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>2380</v>
+        <v>1</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>4484</v>
+        <v>3</v>
       </c>
       <c r="L106" s="20" t="n">
-        <v>5252</v>
+        <v>2</v>
       </c>
       <c r="M106" s="20" t="n">
-        <v>3974</v>
+        <v>5</v>
       </c>
       <c r="N106" s="20" t="n">
-        <v>3256</v>
+        <v>3</v>
       </c>
       <c r="T106" s="20" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="U106" s="20" t="n">
-        <v>-464</v>
+        <v>2</v>
       </c>
       <c r="V106" s="20" t="n">
-        <v>3506</v>
+        <v>1</v>
       </c>
       <c r="W106" s="20" t="n">
-        <v>3411</v>
+        <v>2</v>
       </c>
       <c r="X106" s="20" t="n">
-        <v>3974</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C107" s="20" t="n">
-        <v>-425</v>
-      </c>
-      <c r="D107" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E107" s="20" t="n">
-        <v>-385</v>
-      </c>
-      <c r="F107" s="20" t="n">
-        <v>600</v>
-      </c>
-      <c r="G107" s="20" t="n">
-        <v>-447</v>
-      </c>
-      <c r="H107" s="20" t="n">
-        <v>228</v>
-      </c>
-      <c r="I107" s="20" t="n">
-        <v>-829</v>
-      </c>
-      <c r="J107" s="20" t="n">
-        <v>1279</v>
-      </c>
-      <c r="K107" s="20" t="n">
-        <v>-729</v>
-      </c>
-      <c r="L107" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="M107" s="20" t="n">
-        <v>-935</v>
-      </c>
-      <c r="N107" s="20" t="n">
-        <v>1586</v>
-      </c>
-      <c r="T107" s="20" t="n">
-        <v>-346</v>
-      </c>
-      <c r="U107" s="20" t="n">
-        <v>-259</v>
-      </c>
-      <c r="V107" s="20" t="n">
-        <v>-385</v>
-      </c>
-      <c r="W107" s="20" t="n">
-        <v>-829</v>
-      </c>
-      <c r="X107" s="20" t="n">
-        <v>-935</v>
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>9604</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>8785</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>11353</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>19155</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>8350</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>18972</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>11830</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>14536</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="L107" s="12" t="n">
+        <v>11293</v>
+      </c>
+      <c r="M107" s="12" t="n">
+        <v>11792</v>
+      </c>
+      <c r="N107" s="12" t="n">
+        <v>18532</v>
+      </c>
+      <c r="T107" s="12" t="n">
+        <v>3172</v>
+      </c>
+      <c r="U107" s="12" t="n">
+        <v>-2382</v>
+      </c>
+      <c r="V107" s="12" t="n">
+        <v>11353</v>
+      </c>
+      <c r="W107" s="12" t="n">
+        <v>11830</v>
+      </c>
+      <c r="X107" s="12" t="n">
+        <v>11792</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="n">
+        <v>3044</v>
+      </c>
+      <c r="D108" s="20" t="n">
+        <v>2192</v>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>3506</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>4491</v>
+      </c>
+      <c r="G108" s="20" t="n">
+        <v>2742</v>
+      </c>
+      <c r="H108" s="20" t="n">
+        <v>5139</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>3411</v>
+      </c>
+      <c r="J108" s="20" t="n">
+        <v>2380</v>
+      </c>
+      <c r="K108" s="20" t="n">
+        <v>4484</v>
+      </c>
+      <c r="L108" s="20" t="n">
+        <v>5252</v>
+      </c>
+      <c r="M108" s="20" t="n">
+        <v>3974</v>
+      </c>
+      <c r="N108" s="20" t="n">
+        <v>3256</v>
+      </c>
+      <c r="T108" s="20" t="n">
+        <v>816</v>
+      </c>
+      <c r="U108" s="20" t="n">
+        <v>-464</v>
+      </c>
+      <c r="V108" s="20" t="n">
+        <v>3506</v>
+      </c>
+      <c r="W108" s="20" t="n">
+        <v>3411</v>
+      </c>
+      <c r="X108" s="20" t="n">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="n">
+        <v>-425</v>
+      </c>
+      <c r="D109" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>-385</v>
+      </c>
+      <c r="F109" s="20" t="n">
+        <v>600</v>
+      </c>
+      <c r="G109" s="20" t="n">
+        <v>-447</v>
+      </c>
+      <c r="H109" s="20" t="n">
+        <v>228</v>
+      </c>
+      <c r="I109" s="20" t="n">
+        <v>-829</v>
+      </c>
+      <c r="J109" s="20" t="n">
+        <v>1279</v>
+      </c>
+      <c r="K109" s="20" t="n">
+        <v>-729</v>
+      </c>
+      <c r="L109" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="M109" s="20" t="n">
+        <v>-935</v>
+      </c>
+      <c r="N109" s="20" t="n">
+        <v>1586</v>
+      </c>
+      <c r="T109" s="20" t="n">
+        <v>-346</v>
+      </c>
+      <c r="U109" s="20" t="n">
+        <v>-259</v>
+      </c>
+      <c r="V109" s="20" t="n">
+        <v>-385</v>
+      </c>
+      <c r="W109" s="20" t="n">
+        <v>-829</v>
+      </c>
+      <c r="X109" s="20" t="n">
+        <v>-935</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C108" s="20" t="n">
+      <c r="C110" s="20" t="n">
         <v>2618</v>
       </c>
-      <c r="D108" s="20" t="n">
+      <c r="D110" s="20" t="n">
         <v>2199</v>
       </c>
-      <c r="E108" s="20" t="n">
+      <c r="E110" s="20" t="n">
         <v>3121</v>
       </c>
-      <c r="F108" s="20" t="n">
+      <c r="F110" s="20" t="n">
         <v>5091</v>
       </c>
-      <c r="G108" s="20" t="n">
+      <c r="G110" s="20" t="n">
         <v>2295</v>
       </c>
-      <c r="H108" s="20" t="n">
+      <c r="H110" s="20" t="n">
         <v>5368</v>
       </c>
-      <c r="I108" s="20" t="n">
+      <c r="I110" s="20" t="n">
         <v>2580</v>
       </c>
-      <c r="J108" s="20" t="n">
+      <c r="J110" s="20" t="n">
         <v>3660</v>
       </c>
-      <c r="K108" s="20" t="n">
+      <c r="K110" s="20" t="n">
         <v>3754</v>
       </c>
-      <c r="L108" s="20" t="n">
+      <c r="L110" s="20" t="n">
         <v>5304</v>
       </c>
-      <c r="M108" s="20" t="n">
+      <c r="M110" s="20" t="n">
         <v>3038</v>
       </c>
-      <c r="N108" s="20" t="n">
+      <c r="N110" s="20" t="n">
         <v>4843</v>
       </c>
-      <c r="T108" s="20" t="n">
+      <c r="T110" s="20" t="n">
         <v>471</v>
       </c>
-      <c r="U108" s="20" t="n">
+      <c r="U110" s="20" t="n">
         <v>-723</v>
       </c>
-      <c r="V108" s="20" t="n">
+      <c r="V110" s="20" t="n">
         <v>3121</v>
       </c>
-      <c r="W108" s="20" t="n">
+      <c r="W110" s="20" t="n">
         <v>2580</v>
       </c>
-      <c r="X108" s="20" t="n">
+      <c r="X110" s="20" t="n">
         <v>3038</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="n">
-        <v>6986</v>
-      </c>
-      <c r="D109" s="12" t="n">
-        <v>6586</v>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>8233</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>14064</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>6055</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>13604</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>9249</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>10875</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>17796</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>5989</v>
-      </c>
-      <c r="M109" s="12" t="n">
-        <v>8754</v>
-      </c>
-      <c r="N109" s="12" t="n">
-        <v>13689</v>
-      </c>
-      <c r="T109" s="12" t="n">
-        <v>2701</v>
-      </c>
-      <c r="U109" s="12" t="n">
-        <v>-1659</v>
-      </c>
-      <c r="V109" s="12" t="n">
-        <v>8233</v>
-      </c>
-      <c r="W109" s="12" t="n">
-        <v>9249</v>
-      </c>
-      <c r="X109" s="12" t="n">
-        <v>8754</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>비지배주주 순이익</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>138</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>132</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>175</v>
-      </c>
-      <c r="T110" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="U110" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V110" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="W110" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="X110" s="12" t="n">
-        <v>132</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>6986</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>6586</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>8233</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>14064</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>6055</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>13604</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>9249</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>10875</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>17796</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>5989</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>8754</v>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>13689</v>
+      </c>
+      <c r="T111" s="12" t="n">
+        <v>2701</v>
+      </c>
+      <c r="U111" s="12" t="n">
+        <v>-1659</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>8233</v>
+      </c>
+      <c r="W111" s="12" t="n">
+        <v>9249</v>
+      </c>
+      <c r="X111" s="12" t="n">
+        <v>8754</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G112" s="15">
+        <f>IF(OR(G111="",C111=""),"",IF(C111&lt;=0,"",IFERROR(G111/C111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H112" s="15">
+        <f>IF(OR(H111="",D111=""),"",IF(D111&lt;=0,"",IFERROR(H111/D111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I112" s="15">
+        <f>IF(OR(I111="",E111=""),"",IF(E111&lt;=0,"",IFERROR(I111/E111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J112" s="15">
+        <f>IF(OR(J111="",F111=""),"",IF(F111&lt;=0,"",IFERROR(J111/F111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K112" s="15">
+        <f>IF(OR(K111="",G111=""),"",IF(G111&lt;=0,"",IFERROR(K111/G111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L112" s="15">
+        <f>IF(OR(L111="",H111=""),"",IF(H111&lt;=0,"",IFERROR(L111/H111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M112" s="15">
+        <f>IF(OR(M111="",I111=""),"",IF(I111&lt;=0,"",IFERROR(M111/I111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N112" s="15">
+        <f>IF(OR(N111="",J111=""),"",IF(J111&lt;=0,"",IFERROR(N111/J111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T112" s="15">
+        <f>IF(OR(T111="",S111=""),"",IF(S111&lt;=0,"",IFERROR(T111/S111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U112" s="15">
+        <f>IF(OR(U111="",T111=""),"",IF(T111&lt;=0,"",IFERROR(U111/T111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V112" s="15">
+        <f>IF(OR(V111="",U111=""),"",IF(U111&lt;=0,"",IFERROR(V111/U111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W112" s="15">
+        <f>IF(OR(W111="",V111=""),"",IF(V111&lt;=0,"",IFERROR(W111/V111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X112" s="15">
+        <f>IF(OR(X111="",W111=""),"",IF(W111&lt;=0,"",IFERROR(X111/W111-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>비지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="N113" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="T113" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="U113" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C111" s="12" t="n">
+      <c r="C114" s="12" t="n">
         <v>7733</v>
       </c>
-      <c r="D111" s="12" t="n">
+      <c r="D114" s="12" t="n">
         <v>5782</v>
       </c>
-      <c r="E111" s="12" t="n">
+      <c r="E114" s="12" t="n">
         <v>9553</v>
       </c>
-      <c r="F111" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>13927</v>
       </c>
-      <c r="G111" s="12" t="n">
+      <c r="G114" s="12" t="n">
         <v>7233</v>
       </c>
-      <c r="H111" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>12123</v>
       </c>
-      <c r="I111" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>9166</v>
       </c>
-      <c r="J111" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>10737</v>
       </c>
-      <c r="K111" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>11114</v>
       </c>
-      <c r="L111" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>12532</v>
       </c>
-      <c r="M111" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>8623</v>
       </c>
-      <c r="N111" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>13514</v>
       </c>
-      <c r="T111" s="12" t="n">
+      <c r="T114" s="12" t="n">
         <v>4871</v>
       </c>
-      <c r="U111" s="12" t="n">
+      <c r="U114" s="12" t="n">
         <v>-1669</v>
       </c>
-      <c r="V111" s="12" t="n">
+      <c r="V114" s="12" t="n">
         <v>9553</v>
       </c>
-      <c r="W111" s="12" t="n">
+      <c r="W114" s="12" t="n">
         <v>9166</v>
       </c>
-      <c r="X111" s="12" t="n">
+      <c r="X114" s="12" t="n">
         <v>8623</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G115" s="15">
+        <f>IF(OR(G114="",C114=""),"",IF(C114&lt;=0,"",IFERROR(G114/C114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H115" s="15">
+        <f>IF(OR(H114="",D114=""),"",IF(D114&lt;=0,"",IFERROR(H114/D114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I115" s="15">
+        <f>IF(OR(I114="",E114=""),"",IF(E114&lt;=0,"",IFERROR(I114/E114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J115" s="15">
+        <f>IF(OR(J114="",F114=""),"",IF(F114&lt;=0,"",IFERROR(J114/F114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K115" s="15">
+        <f>IF(OR(K114="",G114=""),"",IF(G114&lt;=0,"",IFERROR(K114/G114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L115" s="15">
+        <f>IF(OR(L114="",H114=""),"",IF(H114&lt;=0,"",IFERROR(L114/H114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M115" s="15">
+        <f>IF(OR(M114="",I114=""),"",IF(I114&lt;=0,"",IFERROR(M114/I114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N115" s="15">
+        <f>IF(OR(N114="",J114=""),"",IF(J114&lt;=0,"",IFERROR(N114/J114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T115" s="15">
+        <f>IF(OR(T114="",S114=""),"",IF(S114&lt;=0,"",IFERROR(T114/S114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U115" s="15">
+        <f>IF(OR(U114="",T114=""),"",IF(T114&lt;=0,"",IFERROR(U114/T114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V115" s="15">
+        <f>IF(OR(V114="",U114=""),"",IF(U114&lt;=0,"",IFERROR(V114/U114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W115" s="15">
+        <f>IF(OR(W114="",V114=""),"",IF(V114&lt;=0,"",IFERROR(W114/V114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X115" s="15">
+        <f>IF(OR(X114="",W114=""),"",IF(W114&lt;=0,"",IFERROR(X114/W114-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B113" s="42" t="inlineStr">
+      <c r="B117" s="42" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="16" t="n"/>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="16" t="n"/>
-      <c r="G113" s="16" t="n"/>
-      <c r="H113" s="16" t="n"/>
-      <c r="I113" s="16" t="n"/>
-      <c r="J113" s="16" t="n"/>
-      <c r="K113" s="16" t="n"/>
-      <c r="L113" s="16" t="n"/>
-      <c r="M113" s="16" t="n"/>
-      <c r="N113" s="16" t="n"/>
-      <c r="O113" s="16" t="n"/>
-      <c r="P113" s="16" t="n"/>
-      <c r="Q113" s="16" t="n"/>
-      <c r="R113" s="16" t="n"/>
-      <c r="S113" s="16" t="n"/>
-      <c r="T113" s="16" t="n"/>
-      <c r="U113" s="16" t="n"/>
-      <c r="V113" s="16" t="n"/>
-      <c r="W113" s="16" t="n"/>
-      <c r="X113" s="16" t="n"/>
-      <c r="Y113" s="16" t="n"/>
-      <c r="Z113" s="16" t="n"/>
-      <c r="AA113" s="16" t="n"/>
-      <c r="AB113" s="16" t="n"/>
-      <c r="AC113" s="16" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="C117" s="16" t="n"/>
+      <c r="D117" s="16" t="n"/>
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="16" t="n"/>
+      <c r="G117" s="16" t="n"/>
+      <c r="H117" s="16" t="n"/>
+      <c r="I117" s="16" t="n"/>
+      <c r="J117" s="16" t="n"/>
+      <c r="K117" s="16" t="n"/>
+      <c r="L117" s="16" t="n"/>
+      <c r="M117" s="16" t="n"/>
+      <c r="N117" s="16" t="n"/>
+      <c r="O117" s="16" t="n"/>
+      <c r="P117" s="16" t="n"/>
+      <c r="Q117" s="16" t="n"/>
+      <c r="R117" s="16" t="n"/>
+      <c r="S117" s="16" t="n"/>
+      <c r="T117" s="16" t="n"/>
+      <c r="U117" s="16" t="n"/>
+      <c r="V117" s="16" t="n"/>
+      <c r="W117" s="16" t="n"/>
+      <c r="X117" s="16" t="n"/>
+      <c r="Y117" s="16" t="n"/>
+      <c r="Z117" s="16" t="n"/>
+      <c r="AA117" s="16" t="n"/>
+      <c r="AB117" s="16" t="n"/>
+      <c r="AC117" s="16" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J114" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K114" s="5" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M114" s="5" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N114" s="5" t="inlineStr">
+      <c r="N118" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O114" s="5" t="inlineStr">
+      <c r="O118" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P114" s="5" t="inlineStr">
+      <c r="P118" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q114" s="5" t="inlineStr">
+      <c r="Q118" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R114" s="5" t="inlineStr">
+      <c r="R118" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S114" s="5" t="inlineStr">
+      <c r="S118" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T114" s="5" t="inlineStr">
+      <c r="T118" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U114" s="5" t="inlineStr">
+      <c r="U118" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V114" s="5" t="inlineStr">
+      <c r="V118" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W114" s="5" t="inlineStr">
+      <c r="W118" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X114" s="5" t="inlineStr">
+      <c r="X118" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y114" s="5" t="inlineStr">
+      <c r="Y118" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z114" s="5" t="inlineStr">
+      <c r="Z118" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA114" s="5" t="inlineStr">
+      <c r="AA118" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB114" s="5" t="inlineStr">
+      <c r="AB118" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC114" s="5" t="inlineStr">
+      <c r="AC118" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C115" s="12" t="n">
+      <c r="C119" s="12" t="n">
         <v>7751</v>
       </c>
-      <c r="D115" s="12" t="n">
+      <c r="D119" s="12" t="n">
         <v>5821</v>
       </c>
-      <c r="E115" s="12" t="n">
+      <c r="E119" s="12" t="n">
         <v>9596</v>
       </c>
-      <c r="F115" s="12" t="n">
+      <c r="F119" s="12" t="n">
         <v>14064</v>
       </c>
-      <c r="G115" s="12" t="n">
+      <c r="G119" s="12" t="n">
         <v>7367</v>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H119" s="12" t="n">
         <v>12292</v>
       </c>
-      <c r="I115" s="12" t="n">
+      <c r="I119" s="12" t="n">
         <v>9249</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="J119" s="12" t="n">
         <v>10875</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="K119" s="12" t="n">
         <v>11184</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="L119" s="12" t="n">
         <v>12601</v>
       </c>
-      <c r="M115" s="12" t="n">
+      <c r="M119" s="12" t="n">
         <v>8754</v>
       </c>
-      <c r="N115" s="12" t="n">
+      <c r="N119" s="12" t="n">
         <v>13689</v>
       </c>
-      <c r="T115" s="12" t="n">
+      <c r="T119" s="12" t="n">
         <v>4938</v>
       </c>
-      <c r="U115" s="12" t="n">
+      <c r="U119" s="12" t="n">
         <v>-1659</v>
       </c>
-      <c r="V115" s="12" t="n">
+      <c r="V119" s="12" t="n">
         <v>9596</v>
       </c>
-      <c r="W115" s="12" t="n">
+      <c r="W119" s="12" t="n">
         <v>9249</v>
       </c>
-      <c r="X115" s="12" t="n">
+      <c r="X119" s="12" t="n">
         <v>8754</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>기타포괄손익</t>
-        </is>
-      </c>
-      <c r="C116" s="20" t="n">
-        <v>-101090</v>
-      </c>
-      <c r="D116" s="20" t="n">
-        <v>78698</v>
-      </c>
-      <c r="E116" s="20" t="n">
-        <v>-4715</v>
-      </c>
-      <c r="F116" s="20" t="n">
-        <v>-50677</v>
-      </c>
-      <c r="G116" s="20" t="n">
-        <v>40612</v>
-      </c>
-      <c r="H116" s="20" t="n">
-        <v>-14184</v>
-      </c>
-      <c r="I116" s="20" t="n">
-        <v>-44658</v>
-      </c>
-      <c r="J116" s="20" t="n">
-        <v>37917</v>
-      </c>
-      <c r="K116" s="20" t="n">
-        <v>57968</v>
-      </c>
-      <c r="L116" s="20" t="n">
-        <v>55716</v>
-      </c>
-      <c r="M116" s="20" t="n">
-        <v>-47000</v>
-      </c>
-      <c r="N116" s="20" t="n">
-        <v>68585</v>
-      </c>
-      <c r="T116" s="20" t="n">
-        <v>-166568</v>
-      </c>
-      <c r="U116" s="20" t="n">
-        <v>98066</v>
-      </c>
-      <c r="V116" s="20" t="n">
-        <v>-4715</v>
-      </c>
-      <c r="W116" s="20" t="n">
-        <v>-44658</v>
-      </c>
-      <c r="X116" s="20" t="n">
-        <v>-47000</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C117" s="20" t="n">
-        <v>-195732</v>
-      </c>
-      <c r="D117" s="20" t="n">
-        <v>184685</v>
-      </c>
-      <c r="E117" s="20" t="n">
-        <v>-43544</v>
-      </c>
-      <c r="F117" s="20" t="n">
-        <v>-87592</v>
-      </c>
-      <c r="G117" s="20" t="n">
-        <v>155752</v>
-      </c>
-      <c r="H117" s="20" t="n">
-        <v>-175182</v>
-      </c>
-      <c r="I117" s="20" t="n">
-        <v>-5082</v>
-      </c>
-      <c r="J117" s="20" t="n">
-        <v>34806</v>
-      </c>
-      <c r="K117" s="20" t="n">
-        <v>23898</v>
-      </c>
-      <c r="L117" s="20" t="n">
-        <v>-33108</v>
-      </c>
-      <c r="M117" s="20" t="n">
-        <v>-113197</v>
-      </c>
-      <c r="N117" s="20" t="n">
-        <v>18731</v>
-      </c>
-      <c r="T117" s="20" t="n">
-        <v>-228165</v>
-      </c>
-      <c r="U117" s="20" t="n">
-        <v>155951</v>
-      </c>
-      <c r="V117" s="20" t="n">
-        <v>-43544</v>
-      </c>
-      <c r="W117" s="20" t="n">
-        <v>-5082</v>
-      </c>
-      <c r="X117" s="20" t="n">
-        <v>-113197</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>이연헤지손익</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="n">
-        <v>93515</v>
-      </c>
-      <c r="D118" s="20" t="n">
-        <v>-106195</v>
-      </c>
-      <c r="E118" s="20" t="n">
-        <v>34884</v>
-      </c>
-      <c r="F118" s="20" t="n">
-        <v>36228</v>
-      </c>
-      <c r="G118" s="20" t="n">
-        <v>-115917</v>
-      </c>
-      <c r="H118" s="20" t="n">
-        <v>161692</v>
-      </c>
-      <c r="I118" s="20" t="n">
-        <v>-44792</v>
-      </c>
-      <c r="J118" s="20" t="n">
-        <v>3472</v>
-      </c>
-      <c r="K118" s="20" t="n">
-        <v>33896</v>
-      </c>
-      <c r="L118" s="20" t="n">
-        <v>88744</v>
-      </c>
-      <c r="M118" s="20" t="n">
-        <v>61360</v>
-      </c>
-      <c r="N118" s="20" t="n">
-        <v>50178</v>
-      </c>
-      <c r="T118" s="20" t="n">
-        <v>62019</v>
-      </c>
-      <c r="U118" s="20" t="n">
-        <v>-59538</v>
-      </c>
-      <c r="V118" s="20" t="n">
-        <v>34884</v>
-      </c>
-      <c r="W118" s="20" t="n">
-        <v>-44792</v>
-      </c>
-      <c r="X118" s="20" t="n">
-        <v>61360</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C119" s="20" t="n">
-        <v>938</v>
-      </c>
-      <c r="D119" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="E119" s="20" t="n">
-        <v>-159</v>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>600</v>
-      </c>
-      <c r="G119" s="20" t="n">
-        <v>691</v>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>-780</v>
-      </c>
-      <c r="I119" s="20" t="n">
-        <v>533</v>
-      </c>
-      <c r="J119" s="20" t="n">
-        <v>-340</v>
-      </c>
-      <c r="K119" s="20" t="n">
-        <v>193</v>
-      </c>
-      <c r="L119" s="20" t="n">
-        <v>102</v>
-      </c>
-      <c r="M119" s="20" t="n">
-        <v>637</v>
-      </c>
-      <c r="N119" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="T119" s="20" t="n">
-        <v>255</v>
-      </c>
-      <c r="U119" s="20" t="n">
-        <v>-180</v>
-      </c>
-      <c r="V119" s="20" t="n">
-        <v>-159</v>
-      </c>
-      <c r="W119" s="20" t="n">
-        <v>533</v>
-      </c>
-      <c r="X119" s="20" t="n">
-        <v>637</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
+          <t>기타포괄손익</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="n">
+        <v>-101090</v>
+      </c>
+      <c r="D120" s="20" t="n">
+        <v>78698</v>
+      </c>
+      <c r="E120" s="20" t="n">
+        <v>-4715</v>
+      </c>
+      <c r="F120" s="20" t="n">
+        <v>-50677</v>
+      </c>
+      <c r="G120" s="20" t="n">
+        <v>40612</v>
+      </c>
+      <c r="H120" s="20" t="n">
+        <v>-14184</v>
+      </c>
+      <c r="I120" s="20" t="n">
+        <v>-44658</v>
+      </c>
+      <c r="J120" s="20" t="n">
+        <v>37917</v>
+      </c>
+      <c r="K120" s="20" t="n">
+        <v>57968</v>
+      </c>
+      <c r="L120" s="20" t="n">
+        <v>55716</v>
+      </c>
+      <c r="M120" s="20" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="N120" s="20" t="n">
+        <v>68585</v>
+      </c>
+      <c r="T120" s="20" t="n">
+        <v>-166568</v>
+      </c>
+      <c r="U120" s="20" t="n">
+        <v>98066</v>
+      </c>
+      <c r="V120" s="20" t="n">
+        <v>-4715</v>
+      </c>
+      <c r="W120" s="20" t="n">
+        <v>-44658</v>
+      </c>
+      <c r="X120" s="20" t="n">
+        <v>-47000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>-195732</v>
+      </c>
+      <c r="D121" s="20" t="n">
+        <v>184685</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>-43544</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>-87592</v>
+      </c>
+      <c r="G121" s="20" t="n">
+        <v>155752</v>
+      </c>
+      <c r="H121" s="20" t="n">
+        <v>-175182</v>
+      </c>
+      <c r="I121" s="20" t="n">
+        <v>-5082</v>
+      </c>
+      <c r="J121" s="20" t="n">
+        <v>34806</v>
+      </c>
+      <c r="K121" s="20" t="n">
+        <v>23898</v>
+      </c>
+      <c r="L121" s="20" t="n">
+        <v>-33108</v>
+      </c>
+      <c r="M121" s="20" t="n">
+        <v>-113197</v>
+      </c>
+      <c r="N121" s="20" t="n">
+        <v>18731</v>
+      </c>
+      <c r="T121" s="20" t="n">
+        <v>-228165</v>
+      </c>
+      <c r="U121" s="20" t="n">
+        <v>155951</v>
+      </c>
+      <c r="V121" s="20" t="n">
+        <v>-43544</v>
+      </c>
+      <c r="W121" s="20" t="n">
+        <v>-5082</v>
+      </c>
+      <c r="X121" s="20" t="n">
+        <v>-113197</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>이연헤지손익</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="n">
+        <v>93515</v>
+      </c>
+      <c r="D122" s="20" t="n">
+        <v>-106195</v>
+      </c>
+      <c r="E122" s="20" t="n">
+        <v>34884</v>
+      </c>
+      <c r="F122" s="20" t="n">
+        <v>36228</v>
+      </c>
+      <c r="G122" s="20" t="n">
+        <v>-115917</v>
+      </c>
+      <c r="H122" s="20" t="n">
+        <v>161692</v>
+      </c>
+      <c r="I122" s="20" t="n">
+        <v>-44792</v>
+      </c>
+      <c r="J122" s="20" t="n">
+        <v>3472</v>
+      </c>
+      <c r="K122" s="20" t="n">
+        <v>33896</v>
+      </c>
+      <c r="L122" s="20" t="n">
+        <v>88744</v>
+      </c>
+      <c r="M122" s="20" t="n">
+        <v>61360</v>
+      </c>
+      <c r="N122" s="20" t="n">
+        <v>50178</v>
+      </c>
+      <c r="T122" s="20" t="n">
+        <v>62019</v>
+      </c>
+      <c r="U122" s="20" t="n">
+        <v>-59538</v>
+      </c>
+      <c r="V122" s="20" t="n">
+        <v>34884</v>
+      </c>
+      <c r="W122" s="20" t="n">
+        <v>-44792</v>
+      </c>
+      <c r="X122" s="20" t="n">
+        <v>61360</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="n">
+        <v>938</v>
+      </c>
+      <c r="D123" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E123" s="20" t="n">
+        <v>-159</v>
+      </c>
+      <c r="F123" s="20" t="n">
+        <v>600</v>
+      </c>
+      <c r="G123" s="20" t="n">
+        <v>691</v>
+      </c>
+      <c r="H123" s="20" t="n">
+        <v>-780</v>
+      </c>
+      <c r="I123" s="20" t="n">
+        <v>533</v>
+      </c>
+      <c r="J123" s="20" t="n">
+        <v>-340</v>
+      </c>
+      <c r="K123" s="20" t="n">
+        <v>193</v>
+      </c>
+      <c r="L123" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="M123" s="20" t="n">
+        <v>637</v>
+      </c>
+      <c r="N123" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="T123" s="20" t="n">
+        <v>255</v>
+      </c>
+      <c r="U123" s="20" t="n">
+        <v>-180</v>
+      </c>
+      <c r="V123" s="20" t="n">
+        <v>-159</v>
+      </c>
+      <c r="W123" s="20" t="n">
+        <v>533</v>
+      </c>
+      <c r="X123" s="20" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C120" s="20" t="n">
+      <c r="C124" s="20" t="n">
         <v>188</v>
       </c>
-      <c r="D120" s="20" t="n">
+      <c r="D124" s="20" t="n">
         <v>188</v>
       </c>
-      <c r="E120" s="20" t="n">
+      <c r="E124" s="20" t="n">
         <v>4104</v>
       </c>
-      <c r="F120" s="20" t="n">
+      <c r="F124" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="G120" s="20" t="n">
+      <c r="G124" s="20" t="n">
         <v>86</v>
       </c>
-      <c r="H120" s="20" t="n">
+      <c r="H124" s="20" t="n">
         <v>86</v>
       </c>
-      <c r="I120" s="20" t="n">
+      <c r="I124" s="20" t="n">
         <v>4834</v>
       </c>
-      <c r="J120" s="20" t="n">
+      <c r="J124" s="20" t="n">
         <v>-20</v>
       </c>
-      <c r="K120" s="20" t="n">
+      <c r="K124" s="20" t="n">
         <v>-20</v>
       </c>
-      <c r="L120" s="20" t="n">
+      <c r="L124" s="20" t="n">
         <v>-21</v>
       </c>
-      <c r="M120" s="20" t="n">
+      <c r="M124" s="20" t="n">
         <v>4198</v>
       </c>
-      <c r="N120" s="20" t="n">
+      <c r="N124" s="20" t="n">
         <v>-340</v>
       </c>
-      <c r="T120" s="20" t="n">
+      <c r="T124" s="20" t="n">
         <v>-677</v>
       </c>
-      <c r="U120" s="20" t="n">
+      <c r="U124" s="20" t="n">
         <v>1833</v>
       </c>
-      <c r="V120" s="20" t="n">
+      <c r="V124" s="20" t="n">
         <v>4104</v>
       </c>
-      <c r="W120" s="20" t="n">
+      <c r="W124" s="20" t="n">
         <v>4834</v>
       </c>
-      <c r="X120" s="20" t="n">
+      <c r="X124" s="20" t="n">
         <v>4198</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C121" s="12" t="n">
+      <c r="C125" s="12" t="n">
         <v>-93339</v>
       </c>
-      <c r="D121" s="12" t="n">
+      <c r="D125" s="12" t="n">
         <v>84519</v>
       </c>
-      <c r="E121" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>4881</v>
       </c>
-      <c r="F121" s="12" t="n">
+      <c r="F125" s="12" t="n">
         <v>-36613</v>
       </c>
-      <c r="G121" s="12" t="n">
+      <c r="G125" s="12" t="n">
         <v>47978</v>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>-1892</v>
       </c>
-      <c r="I121" s="12" t="n">
+      <c r="I125" s="12" t="n">
         <v>-35407</v>
       </c>
-      <c r="J121" s="12" t="n">
+      <c r="J125" s="12" t="n">
         <v>48793</v>
       </c>
-      <c r="K121" s="12" t="n">
+      <c r="K125" s="12" t="n">
         <v>69152</v>
       </c>
-      <c r="L121" s="12" t="n">
+      <c r="L125" s="12" t="n">
         <v>68316</v>
       </c>
-      <c r="M121" s="12" t="n">
+      <c r="M125" s="12" t="n">
         <v>-38245</v>
       </c>
-      <c r="N121" s="12" t="n">
+      <c r="N125" s="12" t="n">
         <v>82274</v>
       </c>
-      <c r="T121" s="12" t="n">
+      <c r="T125" s="12" t="n">
         <v>-161629</v>
       </c>
-      <c r="U121" s="12" t="n">
+      <c r="U125" s="12" t="n">
         <v>96408</v>
       </c>
-      <c r="V121" s="12" t="n">
+      <c r="V125" s="12" t="n">
         <v>4881</v>
       </c>
-      <c r="W121" s="12" t="n">
+      <c r="W125" s="12" t="n">
         <v>-35407</v>
       </c>
-      <c r="X121" s="12" t="n">
+      <c r="X125" s="12" t="n">
         <v>-38245</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C122" s="12" t="n">
+      <c r="C126" s="12" t="n">
         <v>-93373</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D126" s="12" t="n">
         <v>84466</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>4549</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F126" s="12" t="n">
         <v>-36757</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="G126" s="12" t="n">
         <v>47837</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H126" s="12" t="n">
         <v>-2069</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I126" s="12" t="n">
         <v>-35732</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J126" s="12" t="n">
         <v>48653</v>
       </c>
-      <c r="K122" s="12" t="n">
+      <c r="K126" s="12" t="n">
         <v>69079</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L126" s="12" t="n">
         <v>68246</v>
       </c>
-      <c r="M122" s="12" t="n">
+      <c r="M126" s="12" t="n">
         <v>-38699</v>
       </c>
-      <c r="N122" s="12" t="n">
+      <c r="N126" s="12" t="n">
         <v>82118</v>
       </c>
-      <c r="T122" s="12" t="n">
+      <c r="T126" s="12" t="n">
         <v>-161645</v>
       </c>
-      <c r="U122" s="12" t="n">
+      <c r="U126" s="12" t="n">
         <v>96291</v>
       </c>
-      <c r="V122" s="12" t="n">
+      <c r="V126" s="12" t="n">
         <v>4549</v>
       </c>
-      <c r="W122" s="12" t="n">
+      <c r="W126" s="12" t="n">
         <v>-35732</v>
       </c>
-      <c r="X122" s="12" t="n">
+      <c r="X126" s="12" t="n">
         <v>-38699</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C123" s="12" t="n">
+      <c r="C127" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D123" s="12" t="n">
+      <c r="D127" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="E123" s="12" t="n">
+      <c r="E127" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="F123" s="12" t="n">
+      <c r="F127" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="G123" s="12" t="n">
+      <c r="G127" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="H123" s="12" t="n">
+      <c r="H127" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="I123" s="12" t="n">
+      <c r="I127" s="12" t="n">
         <v>325</v>
       </c>
-      <c r="J123" s="12" t="n">
+      <c r="J127" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="K123" s="12" t="n">
+      <c r="K127" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="L123" s="12" t="n">
+      <c r="L127" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M123" s="12" t="n">
+      <c r="M127" s="12" t="n">
         <v>453</v>
       </c>
-      <c r="N123" s="12" t="n">
+      <c r="N127" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="T123" s="12" t="n">
+      <c r="T127" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="U123" s="12" t="n">
+      <c r="U127" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="V123" s="12" t="n">
+      <c r="V127" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="W123" s="12" t="n">
+      <c r="W127" s="12" t="n">
         <v>325</v>
       </c>
-      <c r="X123" s="12" t="n">
+      <c r="X127" s="12" t="n">
         <v>453</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="16" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>부문 · 전 항목</t>
         </is>
       </c>
-      <c r="B125" s="42" t="inlineStr">
+      <c r="B129" s="42" t="inlineStr">
         <is>
           <t>부문 · 항목</t>
         </is>
       </c>
-      <c r="C125" s="16" t="n"/>
-      <c r="D125" s="16" t="n"/>
-      <c r="E125" s="16" t="n"/>
-      <c r="F125" s="16" t="n"/>
-      <c r="G125" s="16" t="n"/>
-      <c r="H125" s="16" t="n"/>
-      <c r="I125" s="16" t="n"/>
-      <c r="J125" s="16" t="n"/>
-      <c r="K125" s="16" t="n"/>
-      <c r="L125" s="16" t="n"/>
-      <c r="M125" s="16" t="n"/>
-      <c r="N125" s="16" t="n"/>
-      <c r="O125" s="16" t="n"/>
-      <c r="P125" s="16" t="n"/>
-      <c r="Q125" s="16" t="n"/>
-      <c r="R125" s="16" t="n"/>
-      <c r="S125" s="16" t="n"/>
-      <c r="T125" s="16" t="n"/>
-      <c r="U125" s="16" t="n"/>
-      <c r="V125" s="16" t="n"/>
-      <c r="W125" s="16" t="n"/>
-      <c r="X125" s="16" t="n"/>
-      <c r="Y125" s="16" t="n"/>
-      <c r="Z125" s="16" t="n"/>
-      <c r="AA125" s="16" t="n"/>
-      <c r="AB125" s="16" t="n"/>
-      <c r="AC125" s="16" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="C129" s="16" t="n"/>
+      <c r="D129" s="16" t="n"/>
+      <c r="E129" s="16" t="n"/>
+      <c r="F129" s="16" t="n"/>
+      <c r="G129" s="16" t="n"/>
+      <c r="H129" s="16" t="n"/>
+      <c r="I129" s="16" t="n"/>
+      <c r="J129" s="16" t="n"/>
+      <c r="K129" s="16" t="n"/>
+      <c r="L129" s="16" t="n"/>
+      <c r="M129" s="16" t="n"/>
+      <c r="N129" s="16" t="n"/>
+      <c r="O129" s="16" t="n"/>
+      <c r="P129" s="16" t="n"/>
+      <c r="Q129" s="16" t="n"/>
+      <c r="R129" s="16" t="n"/>
+      <c r="S129" s="16" t="n"/>
+      <c r="T129" s="16" t="n"/>
+      <c r="U129" s="16" t="n"/>
+      <c r="V129" s="16" t="n"/>
+      <c r="W129" s="16" t="n"/>
+      <c r="X129" s="16" t="n"/>
+      <c r="Y129" s="16" t="n"/>
+      <c r="Z129" s="16" t="n"/>
+      <c r="AA129" s="16" t="n"/>
+      <c r="AB129" s="16" t="n"/>
+      <c r="AC129" s="16" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="J130" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr">
+      <c r="K130" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L130" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M126" s="5" t="inlineStr">
+      <c r="M130" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="N130" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O126" s="5" t="inlineStr">
+      <c r="O130" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P126" s="5" t="inlineStr">
+      <c r="P130" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q126" s="5" t="inlineStr">
+      <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R126" s="5" t="inlineStr">
+      <c r="R130" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S126" s="5" t="inlineStr">
+      <c r="S130" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T126" s="5" t="inlineStr">
+      <c r="T130" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U126" s="5" t="inlineStr">
+      <c r="U130" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V126" s="5" t="inlineStr">
+      <c r="V130" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W126" s="5" t="inlineStr">
+      <c r="W130" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X126" s="5" t="inlineStr">
+      <c r="X130" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y126" s="5" t="inlineStr">
+      <c r="Y130" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z126" s="5" t="inlineStr">
+      <c r="Z130" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA126" s="5" t="inlineStr">
+      <c r="AA130" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB126" s="5" t="inlineStr">
+      <c r="AB130" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC126" s="5" t="inlineStr">
+      <c r="AC130" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="18" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
         <is>
           <t>신금중앙금고 사업 · 경상수익</t>
         </is>
       </c>
-      <c r="E127" s="20" t="n">
+      <c r="E131" s="20" t="n">
         <v>111415</v>
       </c>
-      <c r="F127" s="20" t="n">
+      <c r="F131" s="20" t="n">
         <v>102676</v>
       </c>
-      <c r="I127" s="20" t="n">
+      <c r="I131" s="20" t="n">
         <v>128914</v>
       </c>
-      <c r="J127" s="20" t="n">
+      <c r="J131" s="20" t="n">
         <v>149062</v>
       </c>
-      <c r="M127" s="20" t="n">
+      <c r="M131" s="20" t="n">
         <v>165188</v>
       </c>
-      <c r="N127" s="20" t="n">
+      <c r="N131" s="20" t="n">
         <v>183336</v>
       </c>
-      <c r="V127" s="20" t="n">
+      <c r="V131" s="20" t="n">
         <v>111415</v>
       </c>
-      <c r="W127" s="20" t="n">
+      <c r="W131" s="20" t="n">
         <v>128914</v>
       </c>
-      <c r="X127" s="20" t="n">
+      <c r="X131" s="20" t="n">
         <v>165188</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="18" t="inlineStr">
-        <is>
-          <t>기타 · 경상수익</t>
-        </is>
-      </c>
-      <c r="E128" s="20" t="n">
-        <v>10036</v>
-      </c>
-      <c r="F128" s="20" t="n">
-        <v>10178</v>
-      </c>
-      <c r="I128" s="20" t="n">
-        <v>10335</v>
-      </c>
-      <c r="J128" s="20" t="n">
-        <v>10453</v>
-      </c>
-      <c r="M128" s="20" t="n">
-        <v>11367</v>
-      </c>
-      <c r="N128" s="20" t="n">
-        <v>11555</v>
-      </c>
-      <c r="V128" s="20" t="n">
-        <v>10036</v>
-      </c>
-      <c r="W128" s="20" t="n">
-        <v>10335</v>
-      </c>
-      <c r="X128" s="20" t="n">
-        <v>11367</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>합계 · 경상수익</t>
-        </is>
-      </c>
-      <c r="E129" s="20" t="n">
-        <v>121450</v>
-      </c>
-      <c r="F129" s="20" t="n">
-        <v>112854</v>
-      </c>
-      <c r="I129" s="20" t="n">
-        <v>139249</v>
-      </c>
-      <c r="J129" s="20" t="n">
-        <v>159515</v>
-      </c>
-      <c r="M129" s="20" t="n">
-        <v>176555</v>
-      </c>
-      <c r="N129" s="20" t="n">
-        <v>194891</v>
-      </c>
-      <c r="V129" s="20" t="n">
-        <v>121450</v>
-      </c>
-      <c r="W129" s="20" t="n">
-        <v>139249</v>
-      </c>
-      <c r="X129" s="20" t="n">
-        <v>176555</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 경상수익</t>
-        </is>
-      </c>
-      <c r="E130" s="20" t="n">
-        <v>-1301</v>
-      </c>
-      <c r="F130" s="20" t="n">
-        <v>-1486</v>
-      </c>
-      <c r="I130" s="20" t="n">
-        <v>-1284</v>
-      </c>
-      <c r="J130" s="20" t="n">
-        <v>-9017</v>
-      </c>
-      <c r="M130" s="20" t="n">
-        <v>-1458</v>
-      </c>
-      <c r="N130" s="20" t="n">
-        <v>-1810</v>
-      </c>
-      <c r="V130" s="20" t="n">
-        <v>-1301</v>
-      </c>
-      <c r="W130" s="20" t="n">
-        <v>-1284</v>
-      </c>
-      <c r="X130" s="20" t="n">
-        <v>-1458</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>경상수익</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v>120148</v>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>111368</v>
-      </c>
-      <c r="I131" s="12" t="n">
-        <v>137965</v>
-      </c>
-      <c r="J131" s="12" t="n">
-        <v>150498</v>
-      </c>
-      <c r="M131" s="12" t="n">
-        <v>175098</v>
-      </c>
-      <c r="N131" s="12" t="n">
-        <v>193081</v>
-      </c>
-      <c r="V131" s="12" t="n">
-        <v>120148</v>
-      </c>
-      <c r="W131" s="12" t="n">
-        <v>137965</v>
-      </c>
-      <c r="X131" s="12" t="n">
-        <v>175098</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="18" t="inlineStr">
         <is>
-          <t>신금중앙금고 사업 · 부문 이익</t>
+          <t>기타 · 경상수익</t>
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>9314</v>
+        <v>10036</v>
       </c>
       <c r="F132" s="20" t="n">
-        <v>13417</v>
+        <v>10178</v>
       </c>
       <c r="I132" s="20" t="n">
-        <v>8893</v>
+        <v>10335</v>
       </c>
       <c r="J132" s="20" t="n">
-        <v>17941</v>
+        <v>10453</v>
       </c>
       <c r="M132" s="20" t="n">
-        <v>7972</v>
+        <v>11367</v>
       </c>
       <c r="N132" s="20" t="n">
-        <v>13053</v>
+        <v>11555</v>
       </c>
       <c r="V132" s="20" t="n">
-        <v>9314</v>
+        <v>10036</v>
       </c>
       <c r="W132" s="20" t="n">
-        <v>8893</v>
+        <v>10335</v>
       </c>
       <c r="X132" s="20" t="n">
-        <v>7972</v>
+        <v>11367</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>기타 · 부문 이익</t>
+          <t>합계 · 경상수익</t>
         </is>
       </c>
       <c r="E133" s="20" t="n">
-        <v>331</v>
+        <v>121450</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>725</v>
+        <v>112854</v>
       </c>
       <c r="I133" s="20" t="n">
-        <v>377</v>
+        <v>139249</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>577</v>
+        <v>159515</v>
       </c>
       <c r="M133" s="20" t="n">
-        <v>689</v>
+        <v>176555</v>
       </c>
       <c r="N133" s="20" t="n">
-        <v>830</v>
+        <v>194891</v>
       </c>
       <c r="V133" s="20" t="n">
-        <v>331</v>
+        <v>121450</v>
       </c>
       <c r="W133" s="20" t="n">
-        <v>377</v>
+        <v>139249</v>
       </c>
       <c r="X133" s="20" t="n">
-        <v>689</v>
+        <v>176555</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>합계 · 부문 이익</t>
+          <t>조정액 · 경상수익</t>
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>9645</v>
+        <v>-1301</v>
       </c>
       <c r="F134" s="20" t="n">
-        <v>14142</v>
+        <v>-1486</v>
       </c>
       <c r="I134" s="20" t="n">
-        <v>9269</v>
+        <v>-1284</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>18519</v>
+        <v>-9017</v>
       </c>
       <c r="M134" s="20" t="n">
-        <v>8660</v>
+        <v>-1458</v>
       </c>
       <c r="N134" s="20" t="n">
-        <v>13883</v>
+        <v>-1810</v>
       </c>
       <c r="V134" s="20" t="n">
-        <v>9645</v>
+        <v>-1301</v>
       </c>
       <c r="W134" s="20" t="n">
-        <v>9269</v>
+        <v>-1284</v>
       </c>
       <c r="X134" s="20" t="n">
-        <v>8660</v>
+        <v>-1458</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 부문 이익</t>
-        </is>
-      </c>
-      <c r="E135" s="20" t="n">
-        <v>-92</v>
-      </c>
-      <c r="F135" s="20" t="n">
-        <v>-215</v>
-      </c>
-      <c r="I135" s="20" t="n">
-        <v>-103</v>
-      </c>
-      <c r="J135" s="20" t="n">
-        <v>-7781</v>
-      </c>
-      <c r="M135" s="20" t="n">
-        <v>-37</v>
-      </c>
-      <c r="N135" s="20" t="n">
-        <v>-369</v>
-      </c>
-      <c r="V135" s="20" t="n">
-        <v>-92</v>
-      </c>
-      <c r="W135" s="20" t="n">
-        <v>-103</v>
-      </c>
-      <c r="X135" s="20" t="n">
-        <v>-37</v>
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>경상수익</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>120148</v>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>111368</v>
+      </c>
+      <c r="I135" s="12" t="n">
+        <v>137965</v>
+      </c>
+      <c r="J135" s="12" t="n">
+        <v>150498</v>
+      </c>
+      <c r="M135" s="12" t="n">
+        <v>175098</v>
+      </c>
+      <c r="N135" s="12" t="n">
+        <v>193081</v>
+      </c>
+      <c r="V135" s="12" t="n">
+        <v>120148</v>
+      </c>
+      <c r="W135" s="12" t="n">
+        <v>137965</v>
+      </c>
+      <c r="X135" s="12" t="n">
+        <v>175098</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>부문 이익</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="n">
-        <v>9553</v>
-      </c>
-      <c r="F136" s="12" t="n">
-        <v>13927</v>
-      </c>
-      <c r="I136" s="12" t="n">
-        <v>9166</v>
-      </c>
-      <c r="J136" s="12" t="n">
-        <v>10737</v>
-      </c>
-      <c r="M136" s="12" t="n">
-        <v>8623</v>
-      </c>
-      <c r="N136" s="12" t="n">
-        <v>13514</v>
-      </c>
-      <c r="V136" s="12" t="n">
-        <v>9553</v>
-      </c>
-      <c r="W136" s="12" t="n">
-        <v>9166</v>
-      </c>
-      <c r="X136" s="12" t="n">
-        <v>8623</v>
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I136" s="15">
+        <f>IF(OR(I135="",E135=""),"",IF(E135&lt;=0,"",IFERROR(I135/E135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J136" s="15">
+        <f>IF(OR(J135="",F135=""),"",IF(F135&lt;=0,"",IFERROR(J135/F135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M136" s="15">
+        <f>IF(OR(M135="",I135=""),"",IF(I135&lt;=0,"",IFERROR(M135/I135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N136" s="15">
+        <f>IF(OR(N135="",J135=""),"",IF(J135&lt;=0,"",IFERROR(N135/J135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V136" s="15">
+        <f>IF(OR(V135="",U135=""),"",IF(U135&lt;=0,"",IFERROR(V135/U135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W136" s="15">
+        <f>IF(OR(W135="",V135=""),"",IF(V135&lt;=0,"",IFERROR(W135/V135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X136" s="15">
+        <f>IF(OR(X135="",W135=""),"",IF(W135&lt;=0,"",IFERROR(X135/W135-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>신금중앙금고 사업 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="n">
+        <v>9314</v>
+      </c>
+      <c r="F137" s="20" t="n">
+        <v>13417</v>
+      </c>
+      <c r="I137" s="20" t="n">
+        <v>8893</v>
+      </c>
+      <c r="J137" s="20" t="n">
+        <v>17941</v>
+      </c>
+      <c r="M137" s="20" t="n">
+        <v>7972</v>
+      </c>
+      <c r="N137" s="20" t="n">
+        <v>13053</v>
+      </c>
+      <c r="V137" s="20" t="n">
+        <v>9314</v>
+      </c>
+      <c r="W137" s="20" t="n">
+        <v>8893</v>
+      </c>
+      <c r="X137" s="20" t="n">
+        <v>7972</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="16" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B138" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="n"/>
-      <c r="D138" s="16" t="n"/>
-      <c r="E138" s="16" t="n"/>
-      <c r="F138" s="16" t="n"/>
-      <c r="G138" s="16" t="n"/>
-      <c r="H138" s="16" t="n"/>
-      <c r="I138" s="16" t="n"/>
-      <c r="J138" s="16" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="16" t="n"/>
-      <c r="M138" s="16" t="n"/>
-      <c r="N138" s="16" t="n"/>
-      <c r="O138" s="16" t="n"/>
-      <c r="P138" s="16" t="n"/>
-      <c r="Q138" s="16" t="n"/>
-      <c r="R138" s="16" t="n"/>
-      <c r="S138" s="16" t="n"/>
-      <c r="T138" s="16" t="n"/>
-      <c r="U138" s="16" t="n"/>
-      <c r="V138" s="16" t="n"/>
-      <c r="W138" s="16" t="n"/>
-      <c r="X138" s="16" t="n"/>
-      <c r="Y138" s="16" t="n"/>
-      <c r="Z138" s="16" t="n"/>
-      <c r="AA138" s="16" t="n"/>
-      <c r="AB138" s="16" t="n"/>
-      <c r="AC138" s="16" t="n"/>
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I138" s="15">
+        <f>IF(OR(I137="",E137=""),"",IF(E137&lt;=0,"",IFERROR(I137/E137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J138" s="15">
+        <f>IF(OR(J137="",F137=""),"",IF(F137&lt;=0,"",IFERROR(J137/F137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M138" s="15">
+        <f>IF(OR(M137="",I137=""),"",IF(I137&lt;=0,"",IFERROR(M137/I137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N138" s="15">
+        <f>IF(OR(N137="",J137=""),"",IF(J137&lt;=0,"",IFERROR(N137/J137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V138" s="15">
+        <f>IF(OR(V137="",U137=""),"",IF(U137&lt;=0,"",IFERROR(V137/U137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W138" s="15">
+        <f>IF(OR(W137="",V137=""),"",IF(V137&lt;=0,"",IFERROR(W137/V137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X138" s="15">
+        <f>IF(OR(X137="",W137=""),"",IF(W137&lt;=0,"",IFERROR(X137/W137-1,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N139" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O139" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P139" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q139" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R139" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S139" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T139" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U139" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V139" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W139" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X139" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y139" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z139" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA139" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB139" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC139" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>기타 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="n">
+        <v>331</v>
+      </c>
+      <c r="F139" s="20" t="n">
+        <v>725</v>
+      </c>
+      <c r="I139" s="20" t="n">
+        <v>377</v>
+      </c>
+      <c r="J139" s="20" t="n">
+        <v>577</v>
+      </c>
+      <c r="M139" s="20" t="n">
+        <v>689</v>
+      </c>
+      <c r="N139" s="20" t="n">
+        <v>830</v>
+      </c>
+      <c r="V139" s="20" t="n">
+        <v>331</v>
+      </c>
+      <c r="W139" s="20" t="n">
+        <v>377</v>
+      </c>
+      <c r="X139" s="20" t="n">
+        <v>689</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="n">
-        <v>44079</v>
-      </c>
-      <c r="I140" s="12" t="n">
-        <v>58307</v>
-      </c>
-      <c r="M140" s="12" t="n">
-        <v>59171</v>
-      </c>
-      <c r="O140" s="12" t="n">
-        <v>52804</v>
-      </c>
-      <c r="P140" s="12" t="n">
-        <v>62873</v>
-      </c>
-      <c r="Q140" s="12" t="n">
-        <v>61935</v>
-      </c>
-      <c r="R140" s="12" t="n">
-        <v>56358</v>
-      </c>
-      <c r="S140" s="12" t="n">
-        <v>43426</v>
-      </c>
-      <c r="T140" s="12" t="n">
-        <v>48181</v>
-      </c>
-      <c r="U140" s="12" t="n">
-        <v>35650</v>
-      </c>
-      <c r="V140" s="12" t="n">
-        <v>44079</v>
-      </c>
-      <c r="W140" s="12" t="n">
-        <v>58307</v>
-      </c>
-      <c r="X140" s="12" t="n">
-        <v>59171</v>
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I140" s="15">
+        <f>IF(OR(I139="",E139=""),"",IF(E139&lt;=0,"",IFERROR(I139/E139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J140" s="15">
+        <f>IF(OR(J139="",F139=""),"",IF(F139&lt;=0,"",IFERROR(J139/F139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M140" s="15">
+        <f>IF(OR(M139="",I139=""),"",IF(I139&lt;=0,"",IFERROR(M139/I139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N140" s="15">
+        <f>IF(OR(N139="",J139=""),"",IF(J139&lt;=0,"",IFERROR(N139/J139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V140" s="15">
+        <f>IF(OR(V139="",U139=""),"",IF(U139&lt;=0,"",IFERROR(V139/U139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W140" s="15">
+        <f>IF(OR(W139="",V139=""),"",IF(V139&lt;=0,"",IFERROR(W139/V139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X140" s="15">
+        <f>IF(OR(X139="",W139=""),"",IF(W139&lt;=0,"",IFERROR(X139/W139-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="18" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>합계 · 부문 이익</t>
         </is>
       </c>
       <c r="E141" s="20" t="n">
-        <v>10626</v>
+        <v>9645</v>
+      </c>
+      <c r="F141" s="20" t="n">
+        <v>14142</v>
       </c>
       <c r="I141" s="20" t="n">
-        <v>10948</v>
+        <v>9269</v>
+      </c>
+      <c r="J141" s="20" t="n">
+        <v>18519</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>11510</v>
-      </c>
-      <c r="O141" s="20" t="n">
-        <v>10647</v>
-      </c>
-      <c r="P141" s="20" t="n">
-        <v>9691</v>
-      </c>
-      <c r="Q141" s="20" t="n">
-        <v>10260</v>
-      </c>
-      <c r="R141" s="20" t="n">
-        <v>11266</v>
-      </c>
-      <c r="S141" s="20" t="n">
-        <v>10259</v>
-      </c>
-      <c r="T141" s="20" t="n">
-        <v>9776</v>
-      </c>
-      <c r="U141" s="20" t="n">
-        <v>9858</v>
+        <v>8660</v>
+      </c>
+      <c r="N141" s="20" t="n">
+        <v>13883</v>
       </c>
       <c r="V141" s="20" t="n">
-        <v>10626</v>
+        <v>9645</v>
       </c>
       <c r="W141" s="20" t="n">
-        <v>10948</v>
+        <v>9269</v>
       </c>
       <c r="X141" s="20" t="n">
-        <v>11510</v>
+        <v>8660</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="18" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="E142" s="20" t="n">
-        <v>83</v>
-      </c>
-      <c r="I142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q142" s="20" t="n">
-        <v>1567</v>
-      </c>
-      <c r="R142" s="20" t="n">
-        <v>86</v>
-      </c>
-      <c r="S142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="V142" s="20" t="n">
-        <v>83</v>
-      </c>
-      <c r="W142" s="20" t="n">
-        <v>0</v>
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I142" s="15">
+        <f>IF(OR(I141="",E141=""),"",IF(E141&lt;=0,"",IFERROR(I141/E141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J142" s="15">
+        <f>IF(OR(J141="",F141=""),"",IF(F141&lt;=0,"",IFERROR(J141/F141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M142" s="15">
+        <f>IF(OR(M141="",I141=""),"",IF(I141&lt;=0,"",IFERROR(M141/I141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N142" s="15">
+        <f>IF(OR(N141="",J141=""),"",IF(J141&lt;=0,"",IFERROR(N141/J141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V142" s="15">
+        <f>IF(OR(V141="",U141=""),"",IF(U141&lt;=0,"",IFERROR(V141/U141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W142" s="15">
+        <f>IF(OR(W141="",V141=""),"",IF(V141&lt;=0,"",IFERROR(W141/V141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X142" s="15">
+        <f>IF(OR(X141="",W141=""),"",IF(W141&lt;=0,"",IFERROR(X141/W141-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
+          <t>조정액 · 부문 이익</t>
         </is>
       </c>
       <c r="E143" s="20" t="n">
-        <v>-137</v>
+        <v>-92</v>
+      </c>
+      <c r="F143" s="20" t="n">
+        <v>-215</v>
       </c>
       <c r="I143" s="20" t="n">
-        <v>-848</v>
+        <v>-103</v>
+      </c>
+      <c r="J143" s="20" t="n">
+        <v>-7781</v>
       </c>
       <c r="M143" s="20" t="n">
-        <v>679</v>
-      </c>
-      <c r="O143" s="20" t="n">
-        <v>-544</v>
-      </c>
-      <c r="P143" s="20" t="n">
-        <v>-2341</v>
-      </c>
-      <c r="Q143" s="20" t="n">
-        <v>-12919</v>
-      </c>
-      <c r="R143" s="20" t="n">
-        <v>832</v>
-      </c>
-      <c r="S143" s="20" t="n">
-        <v>-1106</v>
-      </c>
-      <c r="T143" s="20" t="n">
-        <v>-4651</v>
-      </c>
-      <c r="U143" s="20" t="n">
-        <v>-1338</v>
+        <v>-37</v>
+      </c>
+      <c r="N143" s="20" t="n">
+        <v>-369</v>
       </c>
       <c r="V143" s="20" t="n">
-        <v>-137</v>
+        <v>-92</v>
       </c>
       <c r="W143" s="20" t="n">
-        <v>-848</v>
+        <v>-103</v>
       </c>
       <c r="X143" s="20" t="n">
-        <v>679</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="18" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E144" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="I144" s="20" t="n">
-        <v>78</v>
-      </c>
-      <c r="M144" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="O144" s="20" t="n">
-        <v>-38</v>
-      </c>
-      <c r="P144" s="20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q144" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="R144" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="S144" s="20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="T144" s="20" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U144" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="V144" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="W144" s="20" t="n">
-        <v>78</v>
-      </c>
-      <c r="X144" s="20" t="n">
-        <v>68</v>
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>부문 이익</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>9553</v>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>13927</v>
+      </c>
+      <c r="I144" s="12" t="n">
+        <v>9166</v>
+      </c>
+      <c r="J144" s="12" t="n">
+        <v>10737</v>
+      </c>
+      <c r="M144" s="12" t="n">
+        <v>8623</v>
+      </c>
+      <c r="N144" s="12" t="n">
+        <v>13514</v>
+      </c>
+      <c r="V144" s="12" t="n">
+        <v>9553</v>
+      </c>
+      <c r="W144" s="12" t="n">
+        <v>9166</v>
+      </c>
+      <c r="X144" s="12" t="n">
+        <v>8623</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E145" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I145" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="M145" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O145" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P145" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q145" s="20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R145" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="S145" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T145" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U145" s="20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V145" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W145" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X145" s="20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="18" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="E146" s="20" t="n">
-        <v>-5883</v>
-      </c>
-      <c r="I146" s="20" t="n">
-        <v>-7319</v>
-      </c>
-      <c r="M146" s="20" t="n">
-        <v>-6467</v>
-      </c>
-      <c r="O146" s="20" t="n">
-        <v>1105</v>
-      </c>
-      <c r="P146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="20" t="n">
-        <v>881</v>
-      </c>
-      <c r="R146" s="20" t="n">
-        <v>2133</v>
-      </c>
-      <c r="S146" s="20" t="n">
-        <v>-2596</v>
-      </c>
-      <c r="T146" s="20" t="n">
-        <v>1148</v>
-      </c>
-      <c r="U146" s="20" t="n">
-        <v>-2792</v>
-      </c>
-      <c r="V146" s="20" t="n">
-        <v>-5883</v>
-      </c>
-      <c r="W146" s="20" t="n">
-        <v>-7319</v>
-      </c>
-      <c r="X146" s="20" t="n">
-        <v>-6467</v>
+      <c r="A145" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I145" s="15">
+        <f>IF(OR(I144="",E144=""),"",IF(E144&lt;=0,"",IFERROR(I144/E144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J145" s="15">
+        <f>IF(OR(J144="",F144=""),"",IF(F144&lt;=0,"",IFERROR(J144/F144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M145" s="15">
+        <f>IF(OR(M144="",I144=""),"",IF(I144&lt;=0,"",IFERROR(M144/I144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N145" s="15">
+        <f>IF(OR(N144="",J144=""),"",IF(J144&lt;=0,"",IFERROR(N144/J144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V145" s="15">
+        <f>IF(OR(V144="",U144=""),"",IF(U144&lt;=0,"",IFERROR(V144/U144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W145" s="15">
+        <f>IF(OR(W144="",V144=""),"",IF(V144&lt;=0,"",IFERROR(W144/V144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X145" s="15">
+        <f>IF(OR(X144="",W144=""),"",IF(W144&lt;=0,"",IFERROR(X144/W144-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="E147" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="I147" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="M147" s="20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O147" s="20" t="n">
-        <v>-18</v>
-      </c>
-      <c r="P147" s="20" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q147" s="20" t="n">
-        <v>-8</v>
-      </c>
-      <c r="R147" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="S147" s="20" t="n">
-        <v>-117</v>
-      </c>
-      <c r="T147" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="U147" s="20" t="n">
-        <v>-58</v>
-      </c>
-      <c r="V147" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="W147" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="X147" s="20" t="n">
-        <v>-3</v>
-      </c>
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B147" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="n"/>
+      <c r="D147" s="16" t="n"/>
+      <c r="E147" s="16" t="n"/>
+      <c r="F147" s="16" t="n"/>
+      <c r="G147" s="16" t="n"/>
+      <c r="H147" s="16" t="n"/>
+      <c r="I147" s="16" t="n"/>
+      <c r="J147" s="16" t="n"/>
+      <c r="K147" s="16" t="n"/>
+      <c r="L147" s="16" t="n"/>
+      <c r="M147" s="16" t="n"/>
+      <c r="N147" s="16" t="n"/>
+      <c r="O147" s="16" t="n"/>
+      <c r="P147" s="16" t="n"/>
+      <c r="Q147" s="16" t="n"/>
+      <c r="R147" s="16" t="n"/>
+      <c r="S147" s="16" t="n"/>
+      <c r="T147" s="16" t="n"/>
+      <c r="U147" s="16" t="n"/>
+      <c r="V147" s="16" t="n"/>
+      <c r="W147" s="16" t="n"/>
+      <c r="X147" s="16" t="n"/>
+      <c r="Y147" s="16" t="n"/>
+      <c r="Z147" s="16" t="n"/>
+      <c r="AA147" s="16" t="n"/>
+      <c r="AB147" s="16" t="n"/>
+      <c r="AC147" s="16" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>자금운용수익</t>
-        </is>
-      </c>
-      <c r="E148" s="20" t="n">
-        <v>-283914</v>
-      </c>
-      <c r="I148" s="20" t="n">
-        <v>-399819</v>
-      </c>
-      <c r="M148" s="20" t="n">
-        <v>-570688</v>
-      </c>
-      <c r="O148" s="20" t="n">
-        <v>-201637</v>
-      </c>
-      <c r="P148" s="20" t="n">
-        <v>-220528</v>
-      </c>
-      <c r="Q148" s="20" t="n">
-        <v>-193754</v>
-      </c>
-      <c r="R148" s="20" t="n">
-        <v>-207202</v>
-      </c>
-      <c r="S148" s="20" t="n">
-        <v>-175162</v>
-      </c>
-      <c r="T148" s="20" t="n">
-        <v>-175199</v>
-      </c>
-      <c r="U148" s="20" t="n">
-        <v>-208252</v>
-      </c>
-      <c r="V148" s="20" t="n">
-        <v>-283914</v>
-      </c>
-      <c r="W148" s="20" t="n">
-        <v>-399819</v>
-      </c>
-      <c r="X148" s="20" t="n">
-        <v>-570688</v>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O148" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P148" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q148" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S148" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T148" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U148" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V148" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W148" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X148" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y148" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z148" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA148" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB148" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC148" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="18" t="inlineStr">
-        <is>
-          <t>자금조달비용</t>
-        </is>
-      </c>
-      <c r="E149" s="20" t="n">
-        <v>177395</v>
-      </c>
-      <c r="I149" s="20" t="n">
-        <v>318691</v>
-      </c>
-      <c r="M149" s="20" t="n">
-        <v>464694</v>
-      </c>
-      <c r="O149" s="20" t="n">
-        <v>122381</v>
-      </c>
-      <c r="P149" s="20" t="n">
-        <v>121559</v>
-      </c>
-      <c r="Q149" s="20" t="n">
-        <v>119534</v>
-      </c>
-      <c r="R149" s="20" t="n">
-        <v>113700</v>
-      </c>
-      <c r="S149" s="20" t="n">
-        <v>83930</v>
-      </c>
-      <c r="T149" s="20" t="n">
-        <v>70183</v>
-      </c>
-      <c r="U149" s="20" t="n">
-        <v>105263</v>
-      </c>
-      <c r="V149" s="20" t="n">
-        <v>177395</v>
-      </c>
-      <c r="W149" s="20" t="n">
-        <v>318691</v>
-      </c>
-      <c r="X149" s="20" t="n">
-        <v>464694</v>
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>44079</v>
+      </c>
+      <c r="I149" s="12" t="n">
+        <v>58307</v>
+      </c>
+      <c r="M149" s="12" t="n">
+        <v>59171</v>
+      </c>
+      <c r="O149" s="12" t="n">
+        <v>52804</v>
+      </c>
+      <c r="P149" s="12" t="n">
+        <v>62873</v>
+      </c>
+      <c r="Q149" s="12" t="n">
+        <v>61935</v>
+      </c>
+      <c r="R149" s="12" t="n">
+        <v>56358</v>
+      </c>
+      <c r="S149" s="12" t="n">
+        <v>43426</v>
+      </c>
+      <c r="T149" s="12" t="n">
+        <v>48181</v>
+      </c>
+      <c r="U149" s="12" t="n">
+        <v>35650</v>
+      </c>
+      <c r="V149" s="12" t="n">
+        <v>44079</v>
+      </c>
+      <c r="W149" s="12" t="n">
+        <v>58307</v>
+      </c>
+      <c r="X149" s="12" t="n">
+        <v>59171</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>유가증권 관련 손익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>105397</v>
+        <v>10626</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>23732</v>
+        <v>10948</v>
       </c>
       <c r="M150" s="20" t="n">
-        <v>55696</v>
+        <v>11510</v>
       </c>
       <c r="O150" s="20" t="n">
-        <v>-32002</v>
+        <v>10647</v>
       </c>
       <c r="P150" s="20" t="n">
-        <v>23339</v>
+        <v>9691</v>
       </c>
       <c r="Q150" s="20" t="n">
-        <v>-767</v>
+        <v>10260</v>
       </c>
       <c r="R150" s="20" t="n">
-        <v>-7908</v>
+        <v>11266</v>
       </c>
       <c r="S150" s="20" t="n">
-        <v>3251</v>
+        <v>10259</v>
       </c>
       <c r="T150" s="20" t="n">
-        <v>37374</v>
+        <v>9776</v>
       </c>
       <c r="U150" s="20" t="n">
-        <v>120682</v>
+        <v>9858</v>
       </c>
       <c r="V150" s="20" t="n">
-        <v>105397</v>
+        <v>10626</v>
       </c>
       <c r="W150" s="20" t="n">
-        <v>23732</v>
+        <v>10948</v>
       </c>
       <c r="X150" s="20" t="n">
-        <v>55696</v>
+        <v>11510</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 운용손익</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="E151" s="20" t="n">
-        <v>-18</v>
+        <v>83</v>
       </c>
       <c r="I151" s="20" t="n">
-        <v>117</v>
-      </c>
-      <c r="M151" s="20" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="O151" s="20" t="n">
-        <v>-224</v>
+        <v>0</v>
       </c>
       <c r="P151" s="20" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="Q151" s="20" t="n">
-        <v>112</v>
+        <v>1567</v>
       </c>
       <c r="R151" s="20" t="n">
-        <v>-529</v>
+        <v>86</v>
       </c>
       <c r="S151" s="20" t="n">
-        <v>-440</v>
+        <v>0</v>
       </c>
       <c r="T151" s="20" t="n">
-        <v>-95</v>
+        <v>0</v>
       </c>
       <c r="U151" s="20" t="n">
-        <v>-2</v>
+        <v>52</v>
       </c>
       <c r="V151" s="20" t="n">
-        <v>-18</v>
+        <v>83</v>
       </c>
       <c r="W151" s="20" t="n">
-        <v>117</v>
-      </c>
-      <c r="X151" s="20" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>외환차손익</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>-317089</v>
+        <v>-137</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>47933</v>
+        <v>-848</v>
       </c>
       <c r="M152" s="20" t="n">
-        <v>-427503</v>
+        <v>679</v>
       </c>
       <c r="O152" s="20" t="n">
-        <v>43797</v>
+        <v>-544</v>
       </c>
       <c r="P152" s="20" t="n">
-        <v>39214</v>
+        <v>-2341</v>
       </c>
       <c r="Q152" s="20" t="n">
-        <v>-13474</v>
+        <v>-12919</v>
       </c>
       <c r="R152" s="20" t="n">
-        <v>67494</v>
+        <v>832</v>
       </c>
       <c r="S152" s="20" t="n">
-        <v>-112246</v>
+        <v>-1106</v>
       </c>
       <c r="T152" s="20" t="n">
-        <v>-199997</v>
+        <v>-4651</v>
       </c>
       <c r="U152" s="20" t="n">
-        <v>-189856</v>
+        <v>-1338</v>
       </c>
       <c r="V152" s="20" t="n">
-        <v>-317089</v>
+        <v>-137</v>
       </c>
       <c r="W152" s="20" t="n">
-        <v>47933</v>
+        <v>-848</v>
       </c>
       <c r="X152" s="20" t="n">
-        <v>-427503</v>
+        <v>679</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>고정자산 처분손익</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E153" s="20" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I153" s="20" t="n">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="M153" s="20" t="n">
-        <v>-3026</v>
+        <v>68</v>
       </c>
       <c r="O153" s="20" t="n">
-        <v>11</v>
+        <v>-38</v>
       </c>
       <c r="P153" s="20" t="n">
-        <v>117</v>
+        <v>-4</v>
       </c>
       <c r="Q153" s="20" t="n">
-        <v>-50</v>
+        <v>57</v>
       </c>
       <c r="R153" s="20" t="n">
-        <v>266</v>
+        <v>33</v>
       </c>
       <c r="S153" s="20" t="n">
-        <v>127</v>
+        <v>-5</v>
       </c>
       <c r="T153" s="20" t="n">
-        <v>-6</v>
+        <v>-18</v>
       </c>
       <c r="U153" s="20" t="n">
-        <v>315</v>
+        <v>-24</v>
       </c>
       <c r="V153" s="20" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="W153" s="20" t="n">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="X153" s="20" t="n">
-        <v>-3026</v>
+        <v>68</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>특정거래 자산 순증감</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>134919</v>
+        <v>1</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>-227601</v>
+        <v>-7</v>
       </c>
       <c r="M154" s="20" t="n">
-        <v>-336989</v>
+        <v>3</v>
       </c>
       <c r="O154" s="20" t="n">
-        <v>42064</v>
+        <v>3</v>
       </c>
       <c r="P154" s="20" t="n">
-        <v>-18336</v>
+        <v>6</v>
       </c>
       <c r="Q154" s="20" t="n">
-        <v>1838</v>
+        <v>-3</v>
       </c>
       <c r="R154" s="20" t="n">
-        <v>-162689</v>
+        <v>4</v>
       </c>
       <c r="S154" s="20" t="n">
-        <v>130844</v>
+        <v>1</v>
       </c>
       <c r="T154" s="20" t="n">
-        <v>-53436</v>
+        <v>2</v>
       </c>
       <c r="U154" s="20" t="n">
-        <v>-151818</v>
+        <v>-4</v>
       </c>
       <c r="V154" s="20" t="n">
-        <v>134919</v>
+        <v>1</v>
       </c>
       <c r="W154" s="20" t="n">
-        <v>-227601</v>
+        <v>-7</v>
       </c>
       <c r="X154" s="20" t="n">
-        <v>-336989</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>특정거래 부채 순증감</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E155" s="20" t="n">
-        <v>68498</v>
+        <v>-5883</v>
       </c>
       <c r="I155" s="20" t="n">
-        <v>133188</v>
+        <v>-7319</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>238289</v>
+        <v>-6467</v>
       </c>
       <c r="O155" s="20" t="n">
-        <v>-45116</v>
+        <v>1105</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>-17709</v>
+        <v>0</v>
       </c>
       <c r="Q155" s="20" t="n">
-        <v>5529</v>
+        <v>881</v>
       </c>
       <c r="R155" s="20" t="n">
-        <v>-34607</v>
+        <v>2133</v>
       </c>
       <c r="S155" s="20" t="n">
-        <v>-5932</v>
+        <v>-2596</v>
       </c>
       <c r="T155" s="20" t="n">
-        <v>-3714</v>
+        <v>1148</v>
       </c>
       <c r="U155" s="20" t="n">
-        <v>58790</v>
+        <v>-2792</v>
       </c>
       <c r="V155" s="20" t="n">
-        <v>68498</v>
+        <v>-5883</v>
       </c>
       <c r="W155" s="20" t="n">
-        <v>133188</v>
+        <v>-7319</v>
       </c>
       <c r="X155" s="20" t="n">
-        <v>238289</v>
+        <v>-6467</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>특정거래 미수금 순증감</t>
-        </is>
+          <t>임원 퇴직위로 충당금 증감</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="20" t="n">
+        <v>-24</v>
+      </c>
+      <c r="M156" s="20" t="n">
+        <v>-3</v>
       </c>
       <c r="O156" s="20" t="n">
-        <v>2579</v>
+        <v>-18</v>
       </c>
       <c r="P156" s="20" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="Q156" s="20" t="n">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="R156" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="S156" s="20" t="n">
+        <v>-117</v>
+      </c>
+      <c r="T156" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="U156" s="20" t="n">
+        <v>-58</v>
+      </c>
+      <c r="V156" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="W156" s="20" t="n">
+        <v>-24</v>
+      </c>
+      <c r="X156" s="20" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>특정거래 미지급금 순증감</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="E157" s="20" t="n">
-        <v>-21825</v>
+        <v>-283914</v>
       </c>
       <c r="I157" s="20" t="n">
-        <v>9349</v>
+        <v>-399819</v>
       </c>
       <c r="M157" s="20" t="n">
-        <v>-11910</v>
+        <v>-570688</v>
       </c>
       <c r="O157" s="20" t="n">
-        <v>0</v>
+        <v>-201637</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>19738</v>
+        <v>-220528</v>
       </c>
       <c r="Q157" s="20" t="n">
-        <v>2877</v>
+        <v>-193754</v>
       </c>
       <c r="R157" s="20" t="n">
-        <v>30515</v>
+        <v>-207202</v>
       </c>
       <c r="S157" s="20" t="n">
-        <v>-9088</v>
+        <v>-175162</v>
       </c>
       <c r="T157" s="20" t="n">
-        <v>-3905</v>
+        <v>-175199</v>
       </c>
       <c r="U157" s="20" t="n">
-        <v>-5243</v>
+        <v>-208252</v>
       </c>
       <c r="V157" s="20" t="n">
-        <v>-21825</v>
+        <v>-283914</v>
       </c>
       <c r="W157" s="20" t="n">
-        <v>9349</v>
+        <v>-399819</v>
       </c>
       <c r="X157" s="20" t="n">
-        <v>-11910</v>
+        <v>-570688</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>대출금 순증감</t>
+          <t>자금조달비용</t>
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>652990</v>
+        <v>177395</v>
       </c>
       <c r="I158" s="20" t="n">
-        <v>-427377</v>
+        <v>318691</v>
       </c>
       <c r="M158" s="20" t="n">
-        <v>-2948408</v>
+        <v>464694</v>
       </c>
       <c r="O158" s="20" t="n">
-        <v>-1231567</v>
+        <v>122381</v>
       </c>
       <c r="P158" s="20" t="n">
-        <v>1042731</v>
+        <v>121559</v>
       </c>
       <c r="Q158" s="20" t="n">
-        <v>-86124</v>
+        <v>119534</v>
       </c>
       <c r="R158" s="20" t="n">
-        <v>-1429337</v>
+        <v>113700</v>
       </c>
       <c r="S158" s="20" t="n">
-        <v>22075</v>
+        <v>83930</v>
       </c>
       <c r="T158" s="20" t="n">
-        <v>691257</v>
+        <v>70183</v>
       </c>
       <c r="U158" s="20" t="n">
-        <v>-1756520</v>
+        <v>105263</v>
       </c>
       <c r="V158" s="20" t="n">
-        <v>652990</v>
+        <v>177395</v>
       </c>
       <c r="W158" s="20" t="n">
-        <v>-427377</v>
+        <v>318691</v>
       </c>
       <c r="X158" s="20" t="n">
-        <v>-2948408</v>
+        <v>464694</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>예금 순증감</t>
+          <t>유가증권 관련 손익</t>
         </is>
       </c>
       <c r="E159" s="20" t="n">
-        <v>-1588321</v>
+        <v>105397</v>
       </c>
       <c r="I159" s="20" t="n">
-        <v>-1759290</v>
+        <v>23732</v>
       </c>
       <c r="M159" s="20" t="n">
-        <v>-1827917</v>
+        <v>55696</v>
       </c>
       <c r="O159" s="20" t="n">
-        <v>1936177</v>
+        <v>-32002</v>
       </c>
       <c r="P159" s="20" t="n">
-        <v>1080882</v>
+        <v>23339</v>
       </c>
       <c r="Q159" s="20" t="n">
-        <v>710341</v>
+        <v>-767</v>
       </c>
       <c r="R159" s="20" t="n">
-        <v>232549</v>
+        <v>-7908</v>
       </c>
       <c r="S159" s="20" t="n">
-        <v>2579025</v>
+        <v>3251</v>
       </c>
       <c r="T159" s="20" t="n">
-        <v>-629069</v>
+        <v>37374</v>
       </c>
       <c r="U159" s="20" t="n">
-        <v>1529014</v>
+        <v>120682</v>
       </c>
       <c r="V159" s="20" t="n">
-        <v>-1588321</v>
+        <v>105397</v>
       </c>
       <c r="W159" s="20" t="n">
-        <v>-1759290</v>
+        <v>23732</v>
       </c>
       <c r="X159" s="20" t="n">
-        <v>-1827917</v>
+        <v>55696</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>양도성예금 순증감</t>
-        </is>
+          <t>금전신탁 운용손익</t>
+        </is>
+      </c>
+      <c r="E160" s="20" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I160" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="M160" s="20" t="n">
+        <v>-18</v>
       </c>
       <c r="O160" s="20" t="n">
-        <v>-90</v>
+        <v>-224</v>
       </c>
       <c r="P160" s="20" t="n">
-        <v>-40</v>
+        <v>128</v>
       </c>
       <c r="Q160" s="20" t="n">
-        <v>0</v>
+        <v>112</v>
+      </c>
+      <c r="R160" s="20" t="n">
+        <v>-529</v>
+      </c>
+      <c r="S160" s="20" t="n">
+        <v>-440</v>
+      </c>
+      <c r="T160" s="20" t="n">
+        <v>-95</v>
+      </c>
+      <c r="U160" s="20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V160" s="20" t="n">
+        <v>-18</v>
+      </c>
+      <c r="W160" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="X160" s="20" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>채권 순증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="E161" s="20" t="n">
-        <v>-150790</v>
+        <v>-317089</v>
       </c>
       <c r="I161" s="20" t="n">
-        <v>-51760</v>
+        <v>47933</v>
       </c>
       <c r="M161" s="20" t="n">
-        <v>-21100</v>
+        <v>-427503</v>
       </c>
       <c r="O161" s="20" t="n">
-        <v>-102920</v>
+        <v>43797</v>
       </c>
       <c r="P161" s="20" t="n">
-        <v>-244510</v>
+        <v>39214</v>
       </c>
       <c r="Q161" s="20" t="n">
-        <v>-221190</v>
+        <v>-13474</v>
       </c>
       <c r="R161" s="20" t="n">
-        <v>-349780</v>
+        <v>67494</v>
       </c>
       <c r="S161" s="20" t="n">
-        <v>-363650</v>
+        <v>-112246</v>
       </c>
       <c r="T161" s="20" t="n">
-        <v>-225500</v>
+        <v>-199997</v>
       </c>
       <c r="U161" s="20" t="n">
-        <v>-92410</v>
+        <v>-189856</v>
       </c>
       <c r="V161" s="20" t="n">
-        <v>-150790</v>
+        <v>-317089</v>
       </c>
       <c r="W161" s="20" t="n">
-        <v>-51760</v>
+        <v>47933</v>
       </c>
       <c r="X161" s="20" t="n">
-        <v>-21100</v>
+        <v>-427503</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>차용금(후순위차입금 제외) 순증감</t>
+          <t>고정자산 처분손익</t>
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>1293800</v>
+        <v>62</v>
       </c>
       <c r="I162" s="20" t="n">
-        <v>-782700</v>
+        <v>272</v>
       </c>
       <c r="M162" s="20" t="n">
-        <v>-749300</v>
+        <v>-3026</v>
       </c>
       <c r="O162" s="20" t="n">
-        <v>482700</v>
+        <v>11</v>
       </c>
       <c r="P162" s="20" t="n">
-        <v>650100</v>
+        <v>117</v>
       </c>
       <c r="Q162" s="20" t="n">
-        <v>556400</v>
+        <v>-50</v>
       </c>
       <c r="R162" s="20" t="n">
-        <v>1283800</v>
+        <v>266</v>
       </c>
       <c r="S162" s="20" t="n">
-        <v>769500</v>
+        <v>127</v>
       </c>
       <c r="T162" s="20" t="n">
-        <v>147400</v>
+        <v>-6</v>
       </c>
       <c r="U162" s="20" t="n">
-        <v>-169200</v>
+        <v>315</v>
       </c>
       <c r="V162" s="20" t="n">
-        <v>1293800</v>
+        <v>62</v>
       </c>
       <c r="W162" s="20" t="n">
-        <v>-782700</v>
+        <v>272</v>
       </c>
       <c r="X162" s="20" t="n">
-        <v>-749300</v>
+        <v>-3026</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>예치금(중앙은행 예치금 제외) 순증감</t>
+          <t>특정거래 자산 순증감</t>
         </is>
       </c>
       <c r="E163" s="20" t="n">
-        <v>7187</v>
+        <v>134919</v>
       </c>
       <c r="I163" s="20" t="n">
-        <v>-74102</v>
+        <v>-227601</v>
       </c>
       <c r="M163" s="20" t="n">
-        <v>96086</v>
+        <v>-336989</v>
       </c>
       <c r="O163" s="20" t="n">
-        <v>35045</v>
+        <v>42064</v>
       </c>
       <c r="P163" s="20" t="n">
-        <v>333793</v>
+        <v>-18336</v>
       </c>
       <c r="Q163" s="20" t="n">
-        <v>116589</v>
+        <v>1838</v>
       </c>
       <c r="R163" s="20" t="n">
-        <v>88688</v>
+        <v>-162689</v>
       </c>
       <c r="S163" s="20" t="n">
-        <v>-166116</v>
+        <v>130844</v>
       </c>
       <c r="T163" s="20" t="n">
-        <v>17661</v>
+        <v>-53436</v>
       </c>
       <c r="U163" s="20" t="n">
-        <v>-147722</v>
+        <v>-151818</v>
       </c>
       <c r="V163" s="20" t="n">
-        <v>7187</v>
+        <v>134919</v>
       </c>
       <c r="W163" s="20" t="n">
-        <v>-74102</v>
+        <v>-227601</v>
       </c>
       <c r="X163" s="20" t="n">
-        <v>96086</v>
+        <v>-336989</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>콜론 등 순증감</t>
+          <t>특정거래 부채 순증감</t>
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>1363757</v>
+        <v>68498</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>-217185</v>
+        <v>133188</v>
       </c>
       <c r="M164" s="20" t="n">
-        <v>-72839</v>
+        <v>238289</v>
       </c>
       <c r="O164" s="20" t="n">
-        <v>-28146</v>
+        <v>-45116</v>
       </c>
       <c r="P164" s="20" t="n">
-        <v>-121024</v>
+        <v>-17709</v>
       </c>
       <c r="Q164" s="20" t="n">
-        <v>-302627</v>
+        <v>5529</v>
       </c>
       <c r="R164" s="20" t="n">
-        <v>677995</v>
+        <v>-34607</v>
       </c>
       <c r="S164" s="20" t="n">
-        <v>-733519</v>
+        <v>-5932</v>
       </c>
       <c r="T164" s="20" t="n">
-        <v>-502301</v>
+        <v>-3714</v>
       </c>
       <c r="U164" s="20" t="n">
-        <v>-504806</v>
+        <v>58790</v>
       </c>
       <c r="V164" s="20" t="n">
-        <v>1363757</v>
+        <v>68498</v>
       </c>
       <c r="W164" s="20" t="n">
-        <v>-217185</v>
+        <v>133188</v>
       </c>
       <c r="X164" s="20" t="n">
-        <v>-72839</v>
+        <v>238289</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>채권대차거래 지급보증금 순증감</t>
-        </is>
-      </c>
-      <c r="E165" s="20" t="n">
-        <v>-10944</v>
-      </c>
-      <c r="I165" s="20" t="n">
-        <v>10944</v>
-      </c>
-      <c r="M165" s="20" t="n">
-        <v>0</v>
+          <t>특정거래 미수금 순증감</t>
+        </is>
       </c>
       <c r="O165" s="20" t="n">
-        <v>34334</v>
+        <v>2579</v>
       </c>
       <c r="P165" s="20" t="n">
-        <v>70866</v>
+        <v>101</v>
       </c>
       <c r="Q165" s="20" t="n">
-        <v>-7889</v>
-      </c>
-      <c r="R165" s="20" t="n">
-        <v>21798</v>
-      </c>
-      <c r="S165" s="20" t="n">
-        <v>1430</v>
-      </c>
-      <c r="T165" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V165" s="20" t="n">
-        <v>-10944</v>
-      </c>
-      <c r="W165" s="20" t="n">
-        <v>10944</v>
-      </c>
-      <c r="X165" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>콜머니 등 순증감</t>
+          <t>특정거래 미지급금 순증감</t>
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>917072</v>
+        <v>-21825</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>2391601</v>
+        <v>9349</v>
       </c>
       <c r="M166" s="20" t="n">
-        <v>209931</v>
+        <v>-11910</v>
       </c>
       <c r="O166" s="20" t="n">
-        <v>98023</v>
+        <v>0</v>
       </c>
       <c r="P166" s="20" t="n">
-        <v>-77538</v>
+        <v>19738</v>
       </c>
       <c r="Q166" s="20" t="n">
-        <v>51969</v>
+        <v>2877</v>
       </c>
       <c r="R166" s="20" t="n">
-        <v>87601</v>
+        <v>30515</v>
       </c>
       <c r="S166" s="20" t="n">
-        <v>18929</v>
+        <v>-9088</v>
       </c>
       <c r="T166" s="20" t="n">
-        <v>903539</v>
+        <v>-3905</v>
       </c>
       <c r="U166" s="20" t="n">
-        <v>1426807</v>
+        <v>-5243</v>
       </c>
       <c r="V166" s="20" t="n">
-        <v>917072</v>
+        <v>-21825</v>
       </c>
       <c r="W166" s="20" t="n">
-        <v>2391601</v>
+        <v>9349</v>
       </c>
       <c r="X166" s="20" t="n">
-        <v>209931</v>
+        <v>-11910</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>채권대차거래 수입담보금 순증감</t>
+          <t>대출금 순증감</t>
         </is>
       </c>
       <c r="E167" s="20" t="n">
-        <v>788963</v>
+        <v>652990</v>
       </c>
       <c r="I167" s="20" t="n">
-        <v>637534</v>
+        <v>-427377</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>214297</v>
+        <v>-2948408</v>
       </c>
       <c r="O167" s="20" t="n">
-        <v>192408</v>
+        <v>-1231567</v>
       </c>
       <c r="P167" s="20" t="n">
-        <v>182054</v>
+        <v>1042731</v>
       </c>
       <c r="Q167" s="20" t="n">
-        <v>-4466</v>
+        <v>-86124</v>
       </c>
       <c r="R167" s="20" t="n">
-        <v>3849</v>
+        <v>-1429337</v>
       </c>
       <c r="S167" s="20" t="n">
-        <v>-85439</v>
+        <v>22075</v>
       </c>
       <c r="T167" s="20" t="n">
-        <v>25606</v>
+        <v>691257</v>
       </c>
       <c r="U167" s="20" t="n">
-        <v>-366429</v>
+        <v>-1756520</v>
       </c>
       <c r="V167" s="20" t="n">
-        <v>788963</v>
+        <v>652990</v>
       </c>
       <c r="W167" s="20" t="n">
-        <v>637534</v>
+        <v>-427377</v>
       </c>
       <c r="X167" s="20" t="n">
-        <v>214297</v>
+        <v>-2948408</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>매입금전채권 순증감</t>
+          <t>예금 순증감</t>
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>-87644</v>
+        <v>-1588321</v>
       </c>
       <c r="I168" s="20" t="n">
-        <v>13826</v>
+        <v>-1759290</v>
       </c>
       <c r="M168" s="20" t="n">
-        <v>56127</v>
+        <v>-1827917</v>
       </c>
       <c r="O168" s="20" t="n">
-        <v>-2788</v>
+        <v>1936177</v>
       </c>
       <c r="P168" s="20" t="n">
-        <v>3117</v>
+        <v>1080882</v>
       </c>
       <c r="Q168" s="20" t="n">
-        <v>-44372</v>
+        <v>710341</v>
       </c>
       <c r="R168" s="20" t="n">
-        <v>-443</v>
+        <v>232549</v>
       </c>
       <c r="S168" s="20" t="n">
-        <v>41866</v>
+        <v>2579025</v>
       </c>
       <c r="T168" s="20" t="n">
-        <v>-24149</v>
+        <v>-629069</v>
       </c>
       <c r="U168" s="20" t="n">
-        <v>32259</v>
+        <v>1529014</v>
       </c>
       <c r="V168" s="20" t="n">
-        <v>-87644</v>
+        <v>-1588321</v>
       </c>
       <c r="W168" s="20" t="n">
-        <v>13826</v>
+        <v>-1759290</v>
       </c>
       <c r="X168" s="20" t="n">
-        <v>56127</v>
+        <v>-1827917</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>외국환(자산) 순증감</t>
-        </is>
-      </c>
-      <c r="E169" s="20" t="n">
-        <v>-765</v>
-      </c>
-      <c r="I169" s="20" t="n">
-        <v>-1729</v>
-      </c>
-      <c r="M169" s="20" t="n">
-        <v>-8607</v>
+          <t>양도성예금 순증감</t>
+        </is>
       </c>
       <c r="O169" s="20" t="n">
-        <v>-6714</v>
+        <v>-90</v>
       </c>
       <c r="P169" s="20" t="n">
-        <v>54</v>
+        <v>-40</v>
       </c>
       <c r="Q169" s="20" t="n">
-        <v>-669</v>
-      </c>
-      <c r="R169" s="20" t="n">
-        <v>-57984</v>
-      </c>
-      <c r="S169" s="20" t="n">
-        <v>58437</v>
-      </c>
-      <c r="T169" s="20" t="n">
-        <v>1054</v>
-      </c>
-      <c r="U169" s="20" t="n">
-        <v>-3078</v>
-      </c>
-      <c r="V169" s="20" t="n">
-        <v>-765</v>
-      </c>
-      <c r="W169" s="20" t="n">
-        <v>-1729</v>
-      </c>
-      <c r="X169" s="20" t="n">
-        <v>-8607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>외국환(부채) 순증감</t>
+          <t>채권 순증감</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>268</v>
+        <v>-150790</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>-22</v>
+        <v>-51760</v>
       </c>
       <c r="M170" s="20" t="n">
-        <v>337</v>
+        <v>-21100</v>
       </c>
       <c r="O170" s="20" t="n">
-        <v>112</v>
+        <v>-102920</v>
       </c>
       <c r="P170" s="20" t="n">
-        <v>78</v>
+        <v>-244510</v>
       </c>
       <c r="Q170" s="20" t="n">
-        <v>949</v>
+        <v>-221190</v>
       </c>
       <c r="R170" s="20" t="n">
-        <v>16</v>
+        <v>-349780</v>
       </c>
       <c r="S170" s="20" t="n">
-        <v>641</v>
+        <v>-363650</v>
       </c>
       <c r="T170" s="20" t="n">
-        <v>-895</v>
+        <v>-225500</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>-507</v>
+        <v>-92410</v>
       </c>
       <c r="V170" s="20" t="n">
-        <v>268</v>
+        <v>-150790</v>
       </c>
       <c r="W170" s="20" t="n">
-        <v>-22</v>
+        <v>-51760</v>
       </c>
       <c r="X170" s="20" t="n">
-        <v>337</v>
+        <v>-21100</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>신탁계정 차변 순증감</t>
+          <t>차용금(후순위차입금 제외) 순증감</t>
         </is>
       </c>
       <c r="E171" s="20" t="n">
-        <v>1883</v>
+        <v>1293800</v>
       </c>
       <c r="I171" s="20" t="n">
-        <v>-1440</v>
+        <v>-782700</v>
       </c>
       <c r="M171" s="20" t="n">
-        <v>-3208</v>
+        <v>-749300</v>
       </c>
       <c r="O171" s="20" t="n">
-        <v>-2964</v>
+        <v>482700</v>
       </c>
       <c r="P171" s="20" t="n">
-        <v>5015</v>
+        <v>650100</v>
       </c>
       <c r="Q171" s="20" t="n">
-        <v>8650</v>
+        <v>556400</v>
       </c>
       <c r="R171" s="20" t="n">
-        <v>7996</v>
+        <v>1283800</v>
       </c>
       <c r="S171" s="20" t="n">
-        <v>8278</v>
+        <v>769500</v>
       </c>
       <c r="T171" s="20" t="n">
-        <v>12520</v>
+        <v>147400</v>
       </c>
       <c r="U171" s="20" t="n">
-        <v>713</v>
+        <v>-169200</v>
       </c>
       <c r="V171" s="20" t="n">
-        <v>1883</v>
+        <v>1293800</v>
       </c>
       <c r="W171" s="20" t="n">
-        <v>-1440</v>
+        <v>-782700</v>
       </c>
       <c r="X171" s="20" t="n">
-        <v>-3208</v>
+        <v>-749300</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>자금운용 수입</t>
+          <t>예치금(중앙은행 예치금 제외) 순증감</t>
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>339793</v>
+        <v>7187</v>
       </c>
       <c r="I172" s="20" t="n">
-        <v>512646</v>
+        <v>-74102</v>
       </c>
       <c r="M172" s="20" t="n">
-        <v>753966</v>
+        <v>96086</v>
       </c>
       <c r="O172" s="20" t="n">
-        <v>268378</v>
+        <v>35045</v>
       </c>
       <c r="P172" s="20" t="n">
-        <v>275967</v>
+        <v>333793</v>
       </c>
       <c r="Q172" s="20" t="n">
-        <v>250883</v>
+        <v>116589</v>
       </c>
       <c r="R172" s="20" t="n">
-        <v>261547</v>
+        <v>88688</v>
       </c>
       <c r="S172" s="20" t="n">
-        <v>216361</v>
+        <v>-166116</v>
       </c>
       <c r="T172" s="20" t="n">
-        <v>198753</v>
+        <v>17661</v>
       </c>
       <c r="U172" s="20" t="n">
-        <v>173377</v>
+        <v>-147722</v>
       </c>
       <c r="V172" s="20" t="n">
-        <v>339793</v>
+        <v>7187</v>
       </c>
       <c r="W172" s="20" t="n">
-        <v>512646</v>
+        <v>-74102</v>
       </c>
       <c r="X172" s="20" t="n">
-        <v>753966</v>
+        <v>96086</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>자금조달 지출</t>
+          <t>콜론 등 순증감</t>
         </is>
       </c>
       <c r="E173" s="20" t="n">
-        <v>-274043</v>
+        <v>1363757</v>
       </c>
       <c r="I173" s="20" t="n">
-        <v>-429643</v>
+        <v>-217185</v>
       </c>
       <c r="M173" s="20" t="n">
-        <v>-628401</v>
+        <v>-72839</v>
       </c>
       <c r="O173" s="20" t="n">
-        <v>-139300</v>
+        <v>-28146</v>
       </c>
       <c r="P173" s="20" t="n">
-        <v>-142068</v>
+        <v>-121024</v>
       </c>
       <c r="Q173" s="20" t="n">
-        <v>-145715</v>
+        <v>-302627</v>
       </c>
       <c r="R173" s="20" t="n">
-        <v>-136007</v>
+        <v>677995</v>
       </c>
       <c r="S173" s="20" t="n">
-        <v>-97318</v>
+        <v>-733519</v>
       </c>
       <c r="T173" s="20" t="n">
-        <v>-75813</v>
+        <v>-502301</v>
       </c>
       <c r="U173" s="20" t="n">
-        <v>-134553</v>
+        <v>-504806</v>
       </c>
       <c r="V173" s="20" t="n">
-        <v>-274043</v>
+        <v>1363757</v>
       </c>
       <c r="W173" s="20" t="n">
-        <v>-429643</v>
+        <v>-217185</v>
       </c>
       <c r="X173" s="20" t="n">
-        <v>-628401</v>
+        <v>-72839</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>채권대차거래 지급보증금 순증감</t>
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>-43609</v>
+        <v>-10944</v>
       </c>
       <c r="I174" s="20" t="n">
-        <v>615813</v>
+        <v>10944</v>
       </c>
       <c r="M174" s="20" t="n">
-        <v>202088</v>
+        <v>0</v>
       </c>
       <c r="O174" s="20" t="n">
-        <v>-352062</v>
+        <v>34334</v>
       </c>
       <c r="P174" s="20" t="n">
-        <v>-516450</v>
+        <v>70866</v>
       </c>
       <c r="Q174" s="20" t="n">
-        <v>-62350</v>
+        <v>-7889</v>
       </c>
       <c r="R174" s="20" t="n">
-        <v>-215922</v>
+        <v>21798</v>
       </c>
       <c r="S174" s="20" t="n">
-        <v>197501</v>
+        <v>1430</v>
       </c>
       <c r="T174" s="20" t="n">
-        <v>50614</v>
+        <v>0</v>
       </c>
       <c r="U174" s="20" t="n">
-        <v>86025</v>
+        <v>0</v>
       </c>
       <c r="V174" s="20" t="n">
-        <v>-43609</v>
+        <v>-10944</v>
       </c>
       <c r="W174" s="20" t="n">
-        <v>615813</v>
+        <v>10944</v>
       </c>
       <c r="X174" s="20" t="n">
-        <v>202088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>콜머니 등 순증감</t>
         </is>
       </c>
       <c r="E175" s="20" t="n">
-        <v>3121891</v>
+        <v>917072</v>
       </c>
       <c r="I175" s="20" t="n">
-        <v>404114</v>
+        <v>2391601</v>
       </c>
       <c r="M175" s="20" t="n">
-        <v>-5253443</v>
+        <v>209931</v>
       </c>
       <c r="O175" s="20" t="n">
-        <v>1176436</v>
+        <v>98023</v>
       </c>
       <c r="P175" s="20" t="n">
-        <v>2561001</v>
+        <v>-77538</v>
       </c>
       <c r="Q175" s="20" t="n">
-        <v>803994</v>
+        <v>51969</v>
       </c>
       <c r="R175" s="20" t="n">
-        <v>346184</v>
+        <v>87601</v>
       </c>
       <c r="S175" s="20" t="n">
-        <v>2433146</v>
+        <v>18929</v>
       </c>
       <c r="T175" s="20" t="n">
-        <v>316356</v>
+        <v>903539</v>
       </c>
       <c r="U175" s="20" t="n">
-        <v>-155807</v>
+        <v>1426807</v>
       </c>
       <c r="V175" s="20" t="n">
-        <v>3121891</v>
+        <v>917072</v>
       </c>
       <c r="W175" s="20" t="n">
-        <v>404114</v>
+        <v>2391601</v>
       </c>
       <c r="X175" s="20" t="n">
-        <v>-5253443</v>
+        <v>209931</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>채권대차거래 수입담보금 순증감</t>
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>-11453</v>
+        <v>788963</v>
       </c>
       <c r="I176" s="20" t="n">
-        <v>-4671</v>
+        <v>637534</v>
       </c>
       <c r="M176" s="20" t="n">
-        <v>-15570</v>
+        <v>214297</v>
       </c>
       <c r="O176" s="20" t="n">
-        <v>-18665</v>
+        <v>192408</v>
       </c>
       <c r="P176" s="20" t="n">
-        <v>-17362</v>
+        <v>182054</v>
       </c>
       <c r="Q176" s="20" t="n">
-        <v>-11141</v>
+        <v>-4466</v>
       </c>
       <c r="R176" s="20" t="n">
-        <v>-13440</v>
+        <v>3849</v>
       </c>
       <c r="S176" s="20" t="n">
-        <v>-16472</v>
+        <v>-85439</v>
       </c>
       <c r="T176" s="20" t="n">
-        <v>-9555</v>
+        <v>25606</v>
       </c>
       <c r="U176" s="20" t="n">
-        <v>-16126</v>
+        <v>-366429</v>
       </c>
       <c r="V176" s="20" t="n">
-        <v>-11453</v>
+        <v>788963</v>
       </c>
       <c r="W176" s="20" t="n">
-        <v>-4671</v>
+        <v>637534</v>
       </c>
       <c r="X176" s="20" t="n">
-        <v>-15570</v>
+        <v>214297</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E177" s="12" t="n">
-        <v>3110438</v>
-      </c>
-      <c r="I177" s="12" t="n">
-        <v>399442</v>
-      </c>
-      <c r="M177" s="12" t="n">
-        <v>-5269014</v>
-      </c>
-      <c r="O177" s="12" t="n">
-        <v>1157771</v>
-      </c>
-      <c r="P177" s="12" t="n">
-        <v>2543638</v>
-      </c>
-      <c r="Q177" s="12" t="n">
-        <v>792853</v>
-      </c>
-      <c r="R177" s="12" t="n">
-        <v>332744</v>
-      </c>
-      <c r="S177" s="12" t="n">
-        <v>2416674</v>
-      </c>
-      <c r="T177" s="12" t="n">
-        <v>306800</v>
-      </c>
-      <c r="U177" s="12" t="n">
-        <v>-171934</v>
-      </c>
-      <c r="V177" s="12" t="n">
-        <v>3110438</v>
-      </c>
-      <c r="W177" s="12" t="n">
-        <v>399442</v>
-      </c>
-      <c r="X177" s="12" t="n">
-        <v>-5269014</v>
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>매입금전채권 순증감</t>
+        </is>
+      </c>
+      <c r="E177" s="20" t="n">
+        <v>-87644</v>
+      </c>
+      <c r="I177" s="20" t="n">
+        <v>13826</v>
+      </c>
+      <c r="M177" s="20" t="n">
+        <v>56127</v>
+      </c>
+      <c r="O177" s="20" t="n">
+        <v>-2788</v>
+      </c>
+      <c r="P177" s="20" t="n">
+        <v>3117</v>
+      </c>
+      <c r="Q177" s="20" t="n">
+        <v>-44372</v>
+      </c>
+      <c r="R177" s="20" t="n">
+        <v>-443</v>
+      </c>
+      <c r="S177" s="20" t="n">
+        <v>41866</v>
+      </c>
+      <c r="T177" s="20" t="n">
+        <v>-24149</v>
+      </c>
+      <c r="U177" s="20" t="n">
+        <v>32259</v>
+      </c>
+      <c r="V177" s="20" t="n">
+        <v>-87644</v>
+      </c>
+      <c r="W177" s="20" t="n">
+        <v>13826</v>
+      </c>
+      <c r="X177" s="20" t="n">
+        <v>56127</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>유가증권 취득</t>
+          <t>외국환(자산) 순증감</t>
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>-8727731</v>
+        <v>-765</v>
       </c>
       <c r="I178" s="20" t="n">
-        <v>-5829763</v>
+        <v>-1729</v>
       </c>
       <c r="M178" s="20" t="n">
-        <v>-3462395</v>
+        <v>-8607</v>
       </c>
       <c r="O178" s="20" t="n">
-        <v>-4333235</v>
+        <v>-6714</v>
       </c>
       <c r="P178" s="20" t="n">
-        <v>-4221520</v>
+        <v>54</v>
       </c>
       <c r="Q178" s="20" t="n">
-        <v>-4304819</v>
+        <v>-669</v>
       </c>
       <c r="R178" s="20" t="n">
-        <v>-3688121</v>
+        <v>-57984</v>
       </c>
       <c r="S178" s="20" t="n">
-        <v>-11019193</v>
+        <v>58437</v>
       </c>
       <c r="T178" s="20" t="n">
-        <v>-9619387</v>
+        <v>1054</v>
       </c>
       <c r="U178" s="20" t="n">
-        <v>-8107365</v>
+        <v>-3078</v>
       </c>
       <c r="V178" s="20" t="n">
-        <v>-8727731</v>
+        <v>-765</v>
       </c>
       <c r="W178" s="20" t="n">
-        <v>-5829763</v>
+        <v>-1729</v>
       </c>
       <c r="X178" s="20" t="n">
-        <v>-3462395</v>
+        <v>-8607</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="18" t="inlineStr">
         <is>
-          <t>유가증권 매각</t>
+          <t>외국환(부채) 순증감</t>
         </is>
       </c>
       <c r="E179" s="20" t="n">
-        <v>2131240</v>
+        <v>268</v>
       </c>
       <c r="I179" s="20" t="n">
-        <v>2519473</v>
+        <v>-22</v>
       </c>
       <c r="M179" s="20" t="n">
-        <v>1016348</v>
+        <v>337</v>
       </c>
       <c r="O179" s="20" t="n">
-        <v>2195709</v>
+        <v>112</v>
       </c>
       <c r="P179" s="20" t="n">
-        <v>2326190</v>
+        <v>78</v>
       </c>
       <c r="Q179" s="20" t="n">
-        <v>2297629</v>
+        <v>949</v>
       </c>
       <c r="R179" s="20" t="n">
-        <v>1437278</v>
+        <v>16</v>
       </c>
       <c r="S179" s="20" t="n">
-        <v>1092846</v>
+        <v>641</v>
       </c>
       <c r="T179" s="20" t="n">
-        <v>2293222</v>
+        <v>-895</v>
       </c>
       <c r="U179" s="20" t="n">
-        <v>4655227</v>
+        <v>-507</v>
       </c>
       <c r="V179" s="20" t="n">
-        <v>2131240</v>
+        <v>268</v>
       </c>
       <c r="W179" s="20" t="n">
-        <v>2519473</v>
+        <v>-22</v>
       </c>
       <c r="X179" s="20" t="n">
-        <v>1016348</v>
+        <v>337</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>유가증권 상환 수입</t>
+          <t>신탁계정 차변 순증감</t>
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>4404449</v>
+        <v>1883</v>
       </c>
       <c r="I180" s="20" t="n">
-        <v>2027310</v>
+        <v>-1440</v>
       </c>
       <c r="M180" s="20" t="n">
-        <v>1624586</v>
+        <v>-3208</v>
       </c>
       <c r="O180" s="20" t="n">
-        <v>2575669</v>
+        <v>-2964</v>
       </c>
       <c r="P180" s="20" t="n">
-        <v>1805703</v>
+        <v>5015</v>
       </c>
       <c r="Q180" s="20" t="n">
-        <v>2607537</v>
+        <v>8650</v>
       </c>
       <c r="R180" s="20" t="n">
-        <v>2182320</v>
+        <v>7996</v>
       </c>
       <c r="S180" s="20" t="n">
-        <v>8902375</v>
+        <v>8278</v>
       </c>
       <c r="T180" s="20" t="n">
-        <v>8773788</v>
+        <v>12520</v>
       </c>
       <c r="U180" s="20" t="n">
-        <v>5723515</v>
+        <v>713</v>
       </c>
       <c r="V180" s="20" t="n">
-        <v>4404449</v>
+        <v>1883</v>
       </c>
       <c r="W180" s="20" t="n">
-        <v>2027310</v>
+        <v>-1440</v>
       </c>
       <c r="X180" s="20" t="n">
-        <v>1624586</v>
+        <v>-3208</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 증가 지출</t>
+          <t>자금운용 수입</t>
         </is>
       </c>
       <c r="E181" s="20" t="n">
-        <v>-6</v>
+        <v>339793</v>
       </c>
       <c r="I181" s="20" t="n">
-        <v>-5000</v>
+        <v>512646</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>-2000</v>
+        <v>753966</v>
       </c>
       <c r="O181" s="20" t="n">
-        <v>-40000</v>
+        <v>268378</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>-100000</v>
+        <v>275967</v>
       </c>
       <c r="Q181" s="20" t="n">
-        <v>-50210</v>
+        <v>250883</v>
       </c>
       <c r="R181" s="20" t="n">
-        <v>-60</v>
+        <v>261547</v>
       </c>
       <c r="S181" s="20" t="n">
-        <v>-10004</v>
+        <v>216361</v>
       </c>
       <c r="T181" s="20" t="n">
-        <v>-10000</v>
+        <v>198753</v>
       </c>
       <c r="U181" s="20" t="n">
-        <v>0</v>
+        <v>173377</v>
       </c>
       <c r="V181" s="20" t="n">
-        <v>-6</v>
+        <v>339793</v>
       </c>
       <c r="W181" s="20" t="n">
-        <v>-5000</v>
+        <v>512646</v>
       </c>
       <c r="X181" s="20" t="n">
-        <v>-2000</v>
+        <v>753966</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 감소 수입</t>
+          <t>자금조달 지출</t>
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>0</v>
+        <v>-274043</v>
       </c>
       <c r="I182" s="20" t="n">
-        <v>34853</v>
+        <v>-429643</v>
       </c>
       <c r="M182" s="20" t="n">
-        <v>2018</v>
+        <v>-628401</v>
       </c>
       <c r="O182" s="20" t="n">
-        <v>112955</v>
+        <v>-139300</v>
       </c>
       <c r="P182" s="20" t="n">
-        <v>0</v>
+        <v>-142068</v>
       </c>
       <c r="Q182" s="20" t="n">
-        <v>0</v>
+        <v>-145715</v>
       </c>
       <c r="R182" s="20" t="n">
-        <v>39839</v>
+        <v>-136007</v>
       </c>
       <c r="S182" s="20" t="n">
-        <v>10000</v>
+        <v>-97318</v>
       </c>
       <c r="T182" s="20" t="n">
-        <v>1</v>
+        <v>-75813</v>
       </c>
       <c r="U182" s="20" t="n">
-        <v>39913</v>
+        <v>-134553</v>
       </c>
       <c r="V182" s="20" t="n">
-        <v>0</v>
+        <v>-274043</v>
       </c>
       <c r="W182" s="20" t="n">
-        <v>34853</v>
+        <v>-429643</v>
       </c>
       <c r="X182" s="20" t="n">
-        <v>2018</v>
+        <v>-628401</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E183" s="20" t="n">
-        <v>-6609</v>
+        <v>-43609</v>
       </c>
       <c r="I183" s="20" t="n">
-        <v>-5886</v>
+        <v>615813</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>-5531</v>
+        <v>202088</v>
       </c>
       <c r="O183" s="20" t="n">
-        <v>-4542</v>
+        <v>-352062</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>-1775</v>
+        <v>-516450</v>
       </c>
       <c r="Q183" s="20" t="n">
-        <v>-11835</v>
+        <v>-62350</v>
       </c>
       <c r="R183" s="20" t="n">
-        <v>-2724</v>
+        <v>-215922</v>
       </c>
       <c r="S183" s="20" t="n">
-        <v>-2729</v>
+        <v>197501</v>
       </c>
       <c r="T183" s="20" t="n">
-        <v>-3776</v>
+        <v>50614</v>
       </c>
       <c r="U183" s="20" t="n">
-        <v>-3458</v>
+        <v>86025</v>
       </c>
       <c r="V183" s="20" t="n">
-        <v>-6609</v>
+        <v>-43609</v>
       </c>
       <c r="W183" s="20" t="n">
-        <v>-5886</v>
+        <v>615813</v>
       </c>
       <c r="X183" s="20" t="n">
-        <v>-5531</v>
+        <v>202088</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>-3985</v>
+        <v>3121891</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>-13212</v>
+        <v>404114</v>
       </c>
       <c r="M184" s="20" t="n">
-        <v>-4802</v>
+        <v>-5253443</v>
       </c>
       <c r="O184" s="20" t="n">
-        <v>-4007</v>
+        <v>1176436</v>
       </c>
       <c r="P184" s="20" t="n">
-        <v>-3416</v>
+        <v>2561001</v>
       </c>
       <c r="Q184" s="20" t="n">
-        <v>-14660</v>
+        <v>803994</v>
       </c>
       <c r="R184" s="20" t="n">
-        <v>-7771</v>
+        <v>346184</v>
       </c>
       <c r="S184" s="20" t="n">
-        <v>-5032</v>
+        <v>2433146</v>
       </c>
       <c r="T184" s="20" t="n">
-        <v>-2957</v>
+        <v>316356</v>
       </c>
       <c r="U184" s="20" t="n">
-        <v>-9522</v>
+        <v>-155807</v>
       </c>
       <c r="V184" s="20" t="n">
-        <v>-3985</v>
+        <v>3121891</v>
       </c>
       <c r="W184" s="20" t="n">
-        <v>-13212</v>
+        <v>404114</v>
       </c>
       <c r="X184" s="20" t="n">
-        <v>-4802</v>
+        <v>-5253443</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="E185" s="20" t="n">
-        <v>0</v>
+        <v>-11453</v>
       </c>
       <c r="I185" s="20" t="n">
-        <v>0</v>
+        <v>-4671</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>200</v>
+        <v>-15570</v>
+      </c>
+      <c r="O185" s="20" t="n">
+        <v>-18665</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0</v>
+        <v>-17362</v>
       </c>
       <c r="Q185" s="20" t="n">
-        <v>153</v>
+        <v>-11141</v>
       </c>
       <c r="R185" s="20" t="n">
-        <v>0</v>
+        <v>-13440</v>
       </c>
       <c r="S185" s="20" t="n">
-        <v>90</v>
+        <v>-16472</v>
       </c>
       <c r="T185" s="20" t="n">
-        <v>260</v>
+        <v>-9555</v>
       </c>
       <c r="U185" s="20" t="n">
-        <v>193</v>
+        <v>-16126</v>
       </c>
       <c r="V185" s="20" t="n">
-        <v>0</v>
+        <v>-11453</v>
       </c>
       <c r="W185" s="20" t="n">
-        <v>0</v>
+        <v>-4671</v>
       </c>
       <c r="X185" s="20" t="n">
-        <v>200</v>
+        <v>-15570</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="18" t="inlineStr">
-        <is>
-          <t>연결범위 변경 자회사 주식 매각</t>
-        </is>
-      </c>
-      <c r="O186" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P186" s="20" t="n">
-        <v>2417</v>
-      </c>
-      <c r="Q186" s="20" t="n">
-        <v>0</v>
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E186" s="12" t="n">
+        <v>3110438</v>
+      </c>
+      <c r="I186" s="12" t="n">
+        <v>399442</v>
+      </c>
+      <c r="M186" s="12" t="n">
+        <v>-5269014</v>
+      </c>
+      <c r="O186" s="12" t="n">
+        <v>1157771</v>
+      </c>
+      <c r="P186" s="12" t="n">
+        <v>2543638</v>
+      </c>
+      <c r="Q186" s="12" t="n">
+        <v>792853</v>
+      </c>
+      <c r="R186" s="12" t="n">
+        <v>332744</v>
+      </c>
+      <c r="S186" s="12" t="n">
+        <v>2416674</v>
+      </c>
+      <c r="T186" s="12" t="n">
+        <v>306800</v>
+      </c>
+      <c r="U186" s="12" t="n">
+        <v>-171934</v>
+      </c>
+      <c r="V186" s="12" t="n">
+        <v>3110438</v>
+      </c>
+      <c r="W186" s="12" t="n">
+        <v>399442</v>
+      </c>
+      <c r="X186" s="12" t="n">
+        <v>-5269014</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E187" s="12" t="n">
-        <v>-2202642</v>
-      </c>
-      <c r="I187" s="12" t="n">
-        <v>-1272224</v>
-      </c>
-      <c r="M187" s="12" t="n">
-        <v>-831575</v>
-      </c>
-      <c r="O187" s="12" t="n">
-        <v>502548</v>
-      </c>
-      <c r="P187" s="12" t="n">
-        <v>-192401</v>
-      </c>
-      <c r="Q187" s="12" t="n">
-        <v>523793</v>
-      </c>
-      <c r="R187" s="12" t="n">
-        <v>-39240</v>
-      </c>
-      <c r="S187" s="12" t="n">
-        <v>-1031648</v>
-      </c>
-      <c r="T187" s="12" t="n">
-        <v>1431150</v>
-      </c>
-      <c r="U187" s="12" t="n">
-        <v>2298503</v>
-      </c>
-      <c r="V187" s="12" t="n">
-        <v>-2202642</v>
-      </c>
-      <c r="W187" s="12" t="n">
-        <v>-1272224</v>
-      </c>
-      <c r="X187" s="12" t="n">
-        <v>-831575</v>
+      <c r="A187" s="18" t="inlineStr">
+        <is>
+          <t>유가증권 취득</t>
+        </is>
+      </c>
+      <c r="E187" s="20" t="n">
+        <v>-8727731</v>
+      </c>
+      <c r="I187" s="20" t="n">
+        <v>-5829763</v>
+      </c>
+      <c r="M187" s="20" t="n">
+        <v>-3462395</v>
+      </c>
+      <c r="O187" s="20" t="n">
+        <v>-4333235</v>
+      </c>
+      <c r="P187" s="20" t="n">
+        <v>-4221520</v>
+      </c>
+      <c r="Q187" s="20" t="n">
+        <v>-4304819</v>
+      </c>
+      <c r="R187" s="20" t="n">
+        <v>-3688121</v>
+      </c>
+      <c r="S187" s="20" t="n">
+        <v>-11019193</v>
+      </c>
+      <c r="T187" s="20" t="n">
+        <v>-9619387</v>
+      </c>
+      <c r="U187" s="20" t="n">
+        <v>-8107365</v>
+      </c>
+      <c r="V187" s="20" t="n">
+        <v>-8727731</v>
+      </c>
+      <c r="W187" s="20" t="n">
+        <v>-5829763</v>
+      </c>
+      <c r="X187" s="20" t="n">
+        <v>-3462395</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>후순위차입금 상환 지출</t>
+          <t>유가증권 매각</t>
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>-162480</v>
+        <v>2131240</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>0</v>
+        <v>2519473</v>
+      </c>
+      <c r="M188" s="20" t="n">
+        <v>1016348</v>
       </c>
       <c r="O188" s="20" t="n">
-        <v>-108150</v>
+        <v>2195709</v>
       </c>
       <c r="P188" s="20" t="n">
-        <v>-216200</v>
+        <v>2326190</v>
       </c>
       <c r="Q188" s="20" t="n">
-        <v>-226990</v>
+        <v>2297629</v>
       </c>
       <c r="R188" s="20" t="n">
-        <v>0</v>
+        <v>1437278</v>
+      </c>
+      <c r="S188" s="20" t="n">
+        <v>1092846</v>
+      </c>
+      <c r="T188" s="20" t="n">
+        <v>2293222</v>
       </c>
       <c r="U188" s="20" t="n">
-        <v>0</v>
+        <v>4655227</v>
       </c>
       <c r="V188" s="20" t="n">
-        <v>-162480</v>
+        <v>2131240</v>
       </c>
       <c r="W188" s="20" t="n">
-        <v>0</v>
+        <v>2519473</v>
+      </c>
+      <c r="X188" s="20" t="n">
+        <v>1016348</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>출자 증액에 따른 수입</t>
+          <t>유가증권 상환 수입</t>
         </is>
       </c>
       <c r="E189" s="20" t="n">
-        <v>200000</v>
+        <v>4404449</v>
+      </c>
+      <c r="I189" s="20" t="n">
+        <v>2027310</v>
+      </c>
+      <c r="M189" s="20" t="n">
+        <v>1624586</v>
+      </c>
+      <c r="O189" s="20" t="n">
+        <v>2575669</v>
+      </c>
+      <c r="P189" s="20" t="n">
+        <v>1805703</v>
+      </c>
+      <c r="Q189" s="20" t="n">
+        <v>2607537</v>
+      </c>
+      <c r="R189" s="20" t="n">
+        <v>2182320</v>
+      </c>
+      <c r="S189" s="20" t="n">
+        <v>8902375</v>
+      </c>
+      <c r="T189" s="20" t="n">
+        <v>8773788</v>
       </c>
       <c r="U189" s="20" t="n">
-        <v>0</v>
+        <v>5723515</v>
       </c>
       <c r="V189" s="20" t="n">
-        <v>200000</v>
+        <v>4404449</v>
+      </c>
+      <c r="W189" s="20" t="n">
+        <v>2027310</v>
+      </c>
+      <c r="X189" s="20" t="n">
+        <v>1624586</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>출자 증액에 따른 수입</t>
+          <t>금전신탁 증가 지출</t>
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>200000</v>
+        <v>-6</v>
       </c>
       <c r="I190" s="20" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M190" s="20" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="O190" s="20" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="P190" s="20" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="Q190" s="20" t="n">
+        <v>-50210</v>
+      </c>
+      <c r="R190" s="20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="S190" s="20" t="n">
+        <v>-10004</v>
+      </c>
+      <c r="T190" s="20" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="U190" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V190" s="20" t="n">
-        <v>200000</v>
+        <v>-6</v>
       </c>
       <c r="W190" s="20" t="n">
-        <v>0</v>
+        <v>-5000</v>
+      </c>
+      <c r="X190" s="20" t="n">
+        <v>-2000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="18" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>금전신탁 감소 수입</t>
         </is>
       </c>
       <c r="E191" s="20" t="n">
-        <v>-19603</v>
+        <v>0</v>
       </c>
       <c r="I191" s="20" t="n">
-        <v>-19628</v>
+        <v>34853</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>-22603</v>
+        <v>2018</v>
       </c>
       <c r="O191" s="20" t="n">
-        <v>-18115</v>
+        <v>112955</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>-19603</v>
+        <v>0</v>
       </c>
       <c r="Q191" s="20" t="n">
-        <v>-19603</v>
+        <v>0</v>
       </c>
       <c r="R191" s="20" t="n">
-        <v>-19603</v>
+        <v>39839</v>
       </c>
       <c r="S191" s="20" t="n">
-        <v>-19603</v>
+        <v>10000</v>
       </c>
       <c r="T191" s="20" t="n">
-        <v>-19603</v>
+        <v>1</v>
       </c>
       <c r="U191" s="20" t="n">
-        <v>-19603</v>
+        <v>39913</v>
       </c>
       <c r="V191" s="20" t="n">
-        <v>-19603</v>
+        <v>0</v>
       </c>
       <c r="W191" s="20" t="n">
-        <v>-19628</v>
+        <v>34853</v>
       </c>
       <c r="X191" s="20" t="n">
-        <v>-22603</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>비지배주주 배당금 지급</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>-66</v>
+        <v>-6609</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>-66</v>
+        <v>-5886</v>
       </c>
       <c r="M192" s="20" t="n">
-        <v>-133</v>
+        <v>-5531</v>
       </c>
       <c r="O192" s="20" t="n">
-        <v>-66</v>
+        <v>-4542</v>
       </c>
       <c r="P192" s="20" t="n">
-        <v>-66</v>
+        <v>-1775</v>
       </c>
       <c r="Q192" s="20" t="n">
-        <v>-66</v>
+        <v>-11835</v>
       </c>
       <c r="R192" s="20" t="n">
-        <v>-66</v>
+        <v>-2724</v>
       </c>
       <c r="S192" s="20" t="n">
-        <v>-133</v>
+        <v>-2729</v>
       </c>
       <c r="T192" s="20" t="n">
-        <v>-66</v>
+        <v>-3776</v>
       </c>
       <c r="U192" s="20" t="n">
-        <v>-66</v>
+        <v>-3458</v>
       </c>
       <c r="V192" s="20" t="n">
-        <v>-66</v>
+        <v>-6609</v>
       </c>
       <c r="W192" s="20" t="n">
-        <v>-66</v>
+        <v>-5886</v>
       </c>
       <c r="X192" s="20" t="n">
-        <v>-133</v>
+        <v>-5531</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E193" s="12" t="n">
-        <v>17849</v>
-      </c>
-      <c r="I193" s="12" t="n">
-        <v>-19694</v>
-      </c>
-      <c r="M193" s="12" t="n">
-        <v>-22737</v>
-      </c>
-      <c r="O193" s="12" t="n">
-        <v>-126332</v>
-      </c>
-      <c r="P193" s="12" t="n">
-        <v>-235870</v>
-      </c>
-      <c r="Q193" s="12" t="n">
-        <v>-246660</v>
-      </c>
-      <c r="R193" s="12" t="n">
-        <v>-19670</v>
-      </c>
-      <c r="S193" s="12" t="n">
-        <v>-19737</v>
-      </c>
-      <c r="T193" s="12" t="n">
-        <v>-19670</v>
-      </c>
-      <c r="U193" s="12" t="n">
-        <v>-19670</v>
-      </c>
-      <c r="V193" s="12" t="n">
-        <v>17849</v>
-      </c>
-      <c r="W193" s="12" t="n">
-        <v>-19694</v>
-      </c>
-      <c r="X193" s="12" t="n">
-        <v>-22737</v>
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="E193" s="20" t="n">
+        <v>-3985</v>
+      </c>
+      <c r="I193" s="20" t="n">
+        <v>-13212</v>
+      </c>
+      <c r="M193" s="20" t="n">
+        <v>-4802</v>
+      </c>
+      <c r="O193" s="20" t="n">
+        <v>-4007</v>
+      </c>
+      <c r="P193" s="20" t="n">
+        <v>-3416</v>
+      </c>
+      <c r="Q193" s="20" t="n">
+        <v>-14660</v>
+      </c>
+      <c r="R193" s="20" t="n">
+        <v>-7771</v>
+      </c>
+      <c r="S193" s="20" t="n">
+        <v>-5032</v>
+      </c>
+      <c r="T193" s="20" t="n">
+        <v>-2957</v>
+      </c>
+      <c r="U193" s="20" t="n">
+        <v>-9522</v>
+      </c>
+      <c r="V193" s="20" t="n">
+        <v>-3985</v>
+      </c>
+      <c r="W193" s="20" t="n">
+        <v>-13212</v>
+      </c>
+      <c r="X193" s="20" t="n">
+        <v>-4802</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="E194" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I194" s="20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M194" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="P194" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O194" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P194" s="20" t="n">
-        <v>-0</v>
-      </c>
       <c r="Q194" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="R194" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="R194" s="20" t="n">
-        <v>-0</v>
-      </c>
       <c r="S194" s="20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T194" s="20" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="U194" s="20" t="n">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="V194" s="20" t="n">
         <v>0</v>
       </c>
       <c r="W194" s="20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X194" s="20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
+          <t>연결범위 변경 자회사 주식 매각</t>
+        </is>
+      </c>
+      <c r="O195" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" s="20" t="n">
+        <v>2417</v>
+      </c>
+      <c r="Q195" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="n">
+        <v>-2202642</v>
+      </c>
+      <c r="I196" s="12" t="n">
+        <v>-1272224</v>
+      </c>
+      <c r="M196" s="12" t="n">
+        <v>-831575</v>
+      </c>
+      <c r="O196" s="12" t="n">
+        <v>502548</v>
+      </c>
+      <c r="P196" s="12" t="n">
+        <v>-192401</v>
+      </c>
+      <c r="Q196" s="12" t="n">
+        <v>523793</v>
+      </c>
+      <c r="R196" s="12" t="n">
+        <v>-39240</v>
+      </c>
+      <c r="S196" s="12" t="n">
+        <v>-1031648</v>
+      </c>
+      <c r="T196" s="12" t="n">
+        <v>1431150</v>
+      </c>
+      <c r="U196" s="12" t="n">
+        <v>2298503</v>
+      </c>
+      <c r="V196" s="12" t="n">
+        <v>-2202642</v>
+      </c>
+      <c r="W196" s="12" t="n">
+        <v>-1272224</v>
+      </c>
+      <c r="X196" s="12" t="n">
+        <v>-831575</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>후순위차입금 상환 지출</t>
+        </is>
+      </c>
+      <c r="E197" s="20" t="n">
+        <v>-162480</v>
+      </c>
+      <c r="I197" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="20" t="n">
+        <v>-108150</v>
+      </c>
+      <c r="P197" s="20" t="n">
+        <v>-216200</v>
+      </c>
+      <c r="Q197" s="20" t="n">
+        <v>-226990</v>
+      </c>
+      <c r="R197" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" s="20" t="n">
+        <v>-162480</v>
+      </c>
+      <c r="W197" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>출자 증액에 따른 수입</t>
+        </is>
+      </c>
+      <c r="E198" s="20" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U198" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" s="20" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>출자 증액에 따른 수입</t>
+        </is>
+      </c>
+      <c r="E199" s="20" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I199" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" s="20" t="n">
+        <v>200000</v>
+      </c>
+      <c r="W199" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="I200" s="20" t="n">
+        <v>-19628</v>
+      </c>
+      <c r="M200" s="20" t="n">
+        <v>-22603</v>
+      </c>
+      <c r="O200" s="20" t="n">
+        <v>-18115</v>
+      </c>
+      <c r="P200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="Q200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="R200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="S200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="T200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="U200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="V200" s="20" t="n">
+        <v>-19603</v>
+      </c>
+      <c r="W200" s="20" t="n">
+        <v>-19628</v>
+      </c>
+      <c r="X200" s="20" t="n">
+        <v>-22603</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>비지배주주 배당금 지급</t>
+        </is>
+      </c>
+      <c r="E201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="M201" s="20" t="n">
+        <v>-133</v>
+      </c>
+      <c r="O201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="P201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="Q201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="R201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="S201" s="20" t="n">
+        <v>-133</v>
+      </c>
+      <c r="T201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="U201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="V201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="W201" s="20" t="n">
+        <v>-66</v>
+      </c>
+      <c r="X201" s="20" t="n">
+        <v>-133</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E202" s="12" t="n">
+        <v>17849</v>
+      </c>
+      <c r="I202" s="12" t="n">
+        <v>-19694</v>
+      </c>
+      <c r="M202" s="12" t="n">
+        <v>-22737</v>
+      </c>
+      <c r="O202" s="12" t="n">
+        <v>-126332</v>
+      </c>
+      <c r="P202" s="12" t="n">
+        <v>-235870</v>
+      </c>
+      <c r="Q202" s="12" t="n">
+        <v>-246660</v>
+      </c>
+      <c r="R202" s="12" t="n">
+        <v>-19670</v>
+      </c>
+      <c r="S202" s="12" t="n">
+        <v>-19737</v>
+      </c>
+      <c r="T202" s="12" t="n">
+        <v>-19670</v>
+      </c>
+      <c r="U202" s="12" t="n">
+        <v>-19670</v>
+      </c>
+      <c r="V202" s="12" t="n">
+        <v>17849</v>
+      </c>
+      <c r="W202" s="12" t="n">
+        <v>-19694</v>
+      </c>
+      <c r="X202" s="12" t="n">
+        <v>-22737</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P203" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V203" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W203" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X203" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E195" s="20" t="n">
+      <c r="E204" s="20" t="n">
         <v>925646</v>
       </c>
-      <c r="I195" s="20" t="n">
+      <c r="I204" s="20" t="n">
         <v>-892476</v>
       </c>
-      <c r="M195" s="20" t="n">
+      <c r="M204" s="20" t="n">
         <v>-6123326</v>
       </c>
-      <c r="O195" s="20" t="n">
+      <c r="O204" s="20" t="n">
         <v>1533987</v>
       </c>
-      <c r="P195" s="20" t="n">
+      <c r="P204" s="20" t="n">
         <v>2115366</v>
       </c>
-      <c r="Q195" s="20" t="n">
+      <c r="Q204" s="20" t="n">
         <v>1069986</v>
       </c>
-      <c r="R195" s="20" t="n">
+      <c r="R204" s="20" t="n">
         <v>273834</v>
       </c>
-      <c r="S195" s="20" t="n">
+      <c r="S204" s="20" t="n">
         <v>1365289</v>
       </c>
-      <c r="T195" s="20" t="n">
+      <c r="T204" s="20" t="n">
         <v>1718281</v>
       </c>
-      <c r="U195" s="20" t="n">
+      <c r="U204" s="20" t="n">
         <v>2106900</v>
       </c>
-      <c r="V195" s="20" t="n">
+      <c r="V204" s="20" t="n">
         <v>925646</v>
       </c>
-      <c r="W195" s="20" t="n">
+      <c r="W204" s="20" t="n">
         <v>-892476</v>
       </c>
-      <c r="X195" s="20" t="n">
+      <c r="X204" s="20" t="n">
         <v>-6123326</v>
       </c>
     </row>
@@ -11414,7 +11877,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -12636,7 +13099,7 @@
       <c r="L42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -12688,7 +13151,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12740,7 +13203,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12792,7 +13255,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12844,7 +13307,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12896,7 +13359,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12948,7 +13411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12958,43 +13421,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="45">
+      <c r="C49" s="46">
         <f>IFERROR(IF((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="46">
+      <c r="E49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="46">
+      <c r="F49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!K47:N47)&lt;4,"",SUM('연간'!K47:N47)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K47:N47)&lt;4,"",SUM('연간'!K47:N47)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="46">
         <f>IFERROR(IF(('연간'!T47)&lt;=0,"적자",H28/('연간'!T47)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="47">
         <f>IFERROR(IF(('연간'!U47)&lt;=0,"적자",I28/('연간'!U47)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="47">
         <f>IFERROR(IF(('연간'!V47)&lt;=0,"적자",J28/('연간'!V47)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="47">
         <f>IFERROR(IF(('연간'!W47)&lt;=0,"적자",K28/('연간'!W47)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <f>IFERROR(IF(('연간'!X47)&lt;=0,"적자",L28/('연간'!X47)),"")</f>
         <v/>
       </c>
@@ -13018,7 +13481,7 @@
       <c r="L50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -13070,7 +13533,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -13122,7 +13585,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -13174,7 +13637,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -13226,7 +13689,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -13278,7 +13741,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -13348,7 +13811,7 @@
       <c r="L57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -13400,7 +13863,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -13410,49 +13873,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="49">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="49">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="49">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="48">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="49">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="48">
+      <c r="J59" s="49">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="48">
+      <c r="K59" s="49">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="48">
+      <c r="L59" s="49">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="A60" s="45" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -13462,49 +13925,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>IFERROR(C9/(IF(COUNT('연간'!G14:J14)&lt;4,"",SUM('연간'!G14:J14)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="48">
+      <c r="D60" s="49">
         <f>IFERROR(D9/(IF(COUNT('연간'!H14:K14)&lt;4,"",SUM('연간'!H14:K14)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="49">
         <f>IFERROR(E9/(IF(COUNT('연간'!I14:L14)&lt;4,"",SUM('연간'!I14:L14)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48">
+      <c r="F60" s="49">
         <f>IFERROR(F9/(IF(COUNT('연간'!J14:M14)&lt;4,"",SUM('연간'!J14:M14)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="49">
         <f>IFERROR(G9/(IF(COUNT('연간'!K14:N14)&lt;4,"",SUM('연간'!K14:N14)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="47">
+      <c r="H60" s="48">
         <f>IFERROR(H9/('연간'!T14)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="49">
         <f>IFERROR(I9/('연간'!U14)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="48">
+      <c r="J60" s="49">
         <f>IFERROR(J9/('연간'!V14)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="48">
+      <c r="K60" s="49">
         <f>IFERROR(K9/('연간'!W14)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="48">
+      <c r="L60" s="49">
         <f>IFERROR(L9/('연간'!X14)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="45" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -13514,49 +13977,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <f>IFERROR(C19/(IF(COUNT('연간'!G14:J14)&lt;4,"",SUM('연간'!G14:J14)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="48">
+      <c r="D61" s="49">
         <f>IFERROR(D19/(IF(COUNT('연간'!H14:K14)&lt;4,"",SUM('연간'!H14:K14)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="49">
         <f>IFERROR(E19/(IF(COUNT('연간'!I14:L14)&lt;4,"",SUM('연간'!I14:L14)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="49">
         <f>IFERROR(F19/(IF(COUNT('연간'!J14:M14)&lt;4,"",SUM('연간'!J14:M14)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="49">
         <f>IFERROR(G19/(IF(COUNT('연간'!K14:N14)&lt;4,"",SUM('연간'!K14:N14)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="47">
+      <c r="H61" s="48">
         <f>IFERROR(H19/('연간'!T14)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="49">
         <f>IFERROR(I19/('연간'!U14)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="48">
+      <c r="J61" s="49">
         <f>IFERROR(J19/('연간'!V14)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="48">
+      <c r="K61" s="49">
         <f>IFERROR(K19/('연간'!W14)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="49">
         <f>IFERROR(L19/('연간'!X14)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -13566,43 +14029,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="49">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="49">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="49">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="48">
+      <c r="G62" s="49">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="47">
+      <c r="H62" s="48">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="49">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="48">
+      <c r="J62" s="49">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="48">
+      <c r="K62" s="49">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="49">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -13626,7 +14089,7 @@
       <c r="L63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -13678,7 +14141,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="A65" s="45" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13730,7 +14193,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="45" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13782,7 +14245,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="45" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -17489,24 +17952,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
